--- a/research/traditional_assets/database/data/colombia/colombia_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_chemical_basic.xlsx
@@ -1133,7 +1133,7 @@
         <v>2.14201183431953</v>
       </c>
       <c r="F2">
-        <v>3.02849221534482</v>
+        <v>3.02849221534481</v>
       </c>
       <c r="G2">
         <v>1.97722567287785</v>
@@ -1169,7 +1169,7 @@
         <v>0.100307213244775</v>
       </c>
       <c r="R2">
-        <v>0.09299278321799941</v>
+        <v>0.0929927832179995</v>
       </c>
       <c r="S2">
         <v>0.0459273673444086</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1080221872245915</v>
+        <v>0.1076733595693055</v>
       </c>
       <c r="C2">
-        <v>48.19400447776163</v>
+        <v>47.87333341934009</v>
       </c>
       <c r="D2">
-        <v>38.19400447776163</v>
+        <v>38.40933341934009</v>
       </c>
       <c r="E2">
-        <v>-19.1</v>
+        <v>-18.564</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.536</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -1451,28 +1451,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0269608</v>
       </c>
       <c r="N2">
-        <v>6.034999999999999</v>
+        <v>6.008039199999999</v>
       </c>
       <c r="O2">
-        <v>2.11225</v>
+        <v>2.102813719999999</v>
       </c>
       <c r="P2">
-        <v>3.92275</v>
+        <v>3.905225479999999</v>
       </c>
       <c r="Q2">
-        <v>9.96275</v>
+        <v>9.94522548</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1080221872245915</v>
+        <v>0.1084307167366722</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9113532417259312</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>223.8435061274146</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1076733595693055</v>
+        <v>0.1073245319140194</v>
       </c>
       <c r="C3">
-        <v>47.87333341934009</v>
+        <v>47.55510407603512</v>
       </c>
       <c r="D3">
-        <v>38.40933341934009</v>
+        <v>38.62710407603512</v>
       </c>
       <c r="E3">
-        <v>-18.564</v>
+        <v>-18.028</v>
       </c>
       <c r="F3">
-        <v>0.536</v>
+        <v>1.072</v>
       </c>
       <c r="G3">
         <v>10</v>
@@ -1533,28 +1533,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M3">
-        <v>0.0269608</v>
+        <v>0.0539216</v>
       </c>
       <c r="N3">
-        <v>6.008039199999999</v>
+        <v>5.981078399999999</v>
       </c>
       <c r="O3">
-        <v>2.102813719999999</v>
+        <v>2.09337744</v>
       </c>
       <c r="P3">
-        <v>3.905225479999999</v>
+        <v>3.88770096</v>
       </c>
       <c r="Q3">
-        <v>9.94522548</v>
+        <v>9.927700959999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1084307167366722</v>
+        <v>0.1088475835857341</v>
       </c>
       <c r="T3">
-        <v>0.9113532417259312</v>
+        <v>0.9174191623165888</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>223.8435061274146</v>
+        <v>111.9217530637073</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1073245319140194</v>
+        <v>0.1069757042587333</v>
       </c>
       <c r="C4">
-        <v>47.55510407603512</v>
+        <v>47.23935821627921</v>
       </c>
       <c r="D4">
-        <v>38.62710407603512</v>
+        <v>38.84735821627921</v>
       </c>
       <c r="E4">
-        <v>-18.028</v>
+        <v>-17.492</v>
       </c>
       <c r="F4">
-        <v>1.072</v>
+        <v>1.608</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -1615,28 +1615,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M4">
-        <v>0.0539216</v>
+        <v>0.08088239999999999</v>
       </c>
       <c r="N4">
-        <v>5.981078399999999</v>
+        <v>5.954117599999999</v>
       </c>
       <c r="O4">
-        <v>2.09337744</v>
+        <v>2.08394116</v>
       </c>
       <c r="P4">
-        <v>3.88770096</v>
+        <v>3.870176439999999</v>
       </c>
       <c r="Q4">
-        <v>9.927700959999999</v>
+        <v>9.910176439999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1088475835857341</v>
+        <v>0.1092730456275601</v>
       </c>
       <c r="T4">
-        <v>0.9174191623165888</v>
+        <v>0.9236101534348888</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>111.9217530637073</v>
+        <v>74.61450204247153</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1069757042587333</v>
+        <v>0.1066268766034472</v>
       </c>
       <c r="C5">
-        <v>47.23935821627921</v>
+        <v>46.92613856663301</v>
       </c>
       <c r="D5">
-        <v>38.84735821627921</v>
+        <v>39.07013856663301</v>
       </c>
       <c r="E5">
-        <v>-17.492</v>
+        <v>-16.956</v>
       </c>
       <c r="F5">
-        <v>1.608</v>
+        <v>2.144</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -1697,28 +1697,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M5">
-        <v>0.08088239999999999</v>
+        <v>0.1078432</v>
       </c>
       <c r="N5">
-        <v>5.954117599999999</v>
+        <v>5.9271568</v>
       </c>
       <c r="O5">
-        <v>2.08394116</v>
+        <v>2.07450488</v>
       </c>
       <c r="P5">
-        <v>3.870176439999999</v>
+        <v>3.85265192</v>
       </c>
       <c r="Q5">
-        <v>9.910176439999999</v>
+        <v>9.89265192</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1092730456275601</v>
+        <v>0.1097073714619242</v>
       </c>
       <c r="T5">
-        <v>0.9236101534348888</v>
+        <v>0.9299301235348202</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>74.61450204247153</v>
+        <v>55.96087653185365</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1066268766034472</v>
+        <v>0.1062780489481612</v>
       </c>
       <c r="C6">
-        <v>46.92613856663301</v>
+        <v>46.61548883941681</v>
       </c>
       <c r="D6">
-        <v>39.07013856663301</v>
+        <v>39.29548883941681</v>
       </c>
       <c r="E6">
-        <v>-16.956</v>
+        <v>-16.42</v>
       </c>
       <c r="F6">
-        <v>2.144</v>
+        <v>2.68</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -1779,28 +1779,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M6">
-        <v>0.1078432</v>
+        <v>0.134804</v>
       </c>
       <c r="N6">
-        <v>5.9271568</v>
+        <v>5.900195999999999</v>
       </c>
       <c r="O6">
-        <v>2.07450488</v>
+        <v>2.0650686</v>
       </c>
       <c r="P6">
-        <v>3.85265192</v>
+        <v>3.8351274</v>
       </c>
       <c r="Q6">
-        <v>9.89265192</v>
+        <v>9.8751274</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1097073714619242</v>
+        <v>0.1101508409980644</v>
       </c>
       <c r="T6">
-        <v>0.9299301235348202</v>
+        <v>0.9363831456368553</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.96087653185365</v>
+        <v>44.76870122548291</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1062780489481612</v>
+        <v>0.1059292212928751</v>
       </c>
       <c r="C7">
-        <v>46.61548883941681</v>
+        <v>46.3074537613041</v>
       </c>
       <c r="D7">
-        <v>39.29548883941681</v>
+        <v>39.5234537613041</v>
       </c>
       <c r="E7">
-        <v>-16.42</v>
+        <v>-15.884</v>
       </c>
       <c r="F7">
-        <v>2.68</v>
+        <v>3.216</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -1861,28 +1861,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M7">
-        <v>0.134804</v>
+        <v>0.1617648</v>
       </c>
       <c r="N7">
-        <v>5.900195999999999</v>
+        <v>5.873235199999999</v>
       </c>
       <c r="O7">
-        <v>2.0650686</v>
+        <v>2.05563232</v>
       </c>
       <c r="P7">
-        <v>3.8351274</v>
+        <v>3.817602879999999</v>
       </c>
       <c r="Q7">
-        <v>9.8751274</v>
+        <v>9.85760288</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1101508409980644</v>
+        <v>0.1106037460562501</v>
       </c>
       <c r="T7">
-        <v>0.9363831456368553</v>
+        <v>0.942973466081487</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.76870122548291</v>
+        <v>37.30725102123576</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1059292212928751</v>
+        <v>0.1055803936375891</v>
       </c>
       <c r="C8">
-        <v>46.3074537613041</v>
+        <v>46.00207910291599</v>
       </c>
       <c r="D8">
-        <v>39.5234537613041</v>
+        <v>39.75407910291599</v>
       </c>
       <c r="E8">
-        <v>-15.884</v>
+        <v>-15.348</v>
       </c>
       <c r="F8">
-        <v>3.216</v>
+        <v>3.752</v>
       </c>
       <c r="G8">
         <v>10</v>
@@ -1943,28 +1943,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M8">
-        <v>0.1617648</v>
+        <v>0.1887256</v>
       </c>
       <c r="N8">
-        <v>5.873235199999999</v>
+        <v>5.8462744</v>
       </c>
       <c r="O8">
-        <v>2.05563232</v>
+        <v>2.04619604</v>
       </c>
       <c r="P8">
-        <v>3.817602879999999</v>
+        <v>3.80007836</v>
       </c>
       <c r="Q8">
-        <v>9.85760288</v>
+        <v>9.84007836</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1106037460562501</v>
+        <v>0.1110663910081603</v>
       </c>
       <c r="T8">
-        <v>0.942973466081487</v>
+        <v>0.9497055138475086</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.30725102123576</v>
+        <v>31.9776437324878</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.105580393637589</v>
+        <v>0.105231565982303</v>
       </c>
       <c r="C9">
-        <v>46.002079102916</v>
+        <v>45.69941170945808</v>
       </c>
       <c r="D9">
-        <v>39.754079102916</v>
+        <v>39.98741170945807</v>
       </c>
       <c r="E9">
-        <v>-15.348</v>
+        <v>-14.812</v>
       </c>
       <c r="F9">
-        <v>3.752000000000001</v>
+        <v>4.288</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -2025,28 +2025,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M9">
-        <v>0.1887256</v>
+        <v>0.2156864</v>
       </c>
       <c r="N9">
-        <v>5.8462744</v>
+        <v>5.819313599999999</v>
       </c>
       <c r="O9">
-        <v>2.04619604</v>
+        <v>2.03675976</v>
       </c>
       <c r="P9">
-        <v>3.80007836</v>
+        <v>3.782553839999999</v>
       </c>
       <c r="Q9">
-        <v>9.84007836</v>
+        <v>9.822553839999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1110663910081603</v>
+        <v>0.111539093459025</v>
       </c>
       <c r="T9">
-        <v>0.9497055138475086</v>
+        <v>0.9565839104780088</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.9776437324878</v>
+        <v>27.98043826592682</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.105231565982303</v>
+        <v>0.1048827383270169</v>
       </c>
       <c r="C10">
-        <v>45.69941170945808</v>
+        <v>45.39949953244223</v>
       </c>
       <c r="D10">
-        <v>39.98741170945807</v>
+        <v>40.22349953244223</v>
       </c>
       <c r="E10">
-        <v>-14.812</v>
+        <v>-14.276</v>
       </c>
       <c r="F10">
-        <v>4.288</v>
+        <v>4.824</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -2107,28 +2107,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M10">
-        <v>0.2156864</v>
+        <v>0.2426472</v>
       </c>
       <c r="N10">
-        <v>5.819313599999999</v>
+        <v>5.792352799999999</v>
       </c>
       <c r="O10">
-        <v>2.03675976</v>
+        <v>2.027323479999999</v>
       </c>
       <c r="P10">
-        <v>3.782553839999999</v>
+        <v>3.76502932</v>
       </c>
       <c r="Q10">
-        <v>9.822553839999999</v>
+        <v>9.805029319999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.111539093459025</v>
+        <v>0.1120221849747438</v>
       </c>
       <c r="T10">
-        <v>0.9565839104780088</v>
+        <v>0.9636134806608279</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.98043826592682</v>
+        <v>24.87150068082384</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1048827383270169</v>
+        <v>0.1045339106717308</v>
       </c>
       <c r="C11">
-        <v>45.39949953244223</v>
+        <v>45.10239166253933</v>
       </c>
       <c r="D11">
-        <v>40.22349953244223</v>
+        <v>40.46239166253932</v>
       </c>
       <c r="E11">
-        <v>-14.276</v>
+        <v>-13.74</v>
       </c>
       <c r="F11">
-        <v>4.824</v>
+        <v>5.359999999999999</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -2189,28 +2189,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M11">
-        <v>0.2426472</v>
+        <v>0.269608</v>
       </c>
       <c r="N11">
-        <v>5.792352799999999</v>
+        <v>5.765391999999999</v>
       </c>
       <c r="O11">
-        <v>2.027323479999999</v>
+        <v>2.0178872</v>
       </c>
       <c r="P11">
-        <v>3.76502932</v>
+        <v>3.7475048</v>
       </c>
       <c r="Q11">
-        <v>9.805029319999999</v>
+        <v>9.787504800000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1120221849747438</v>
+        <v>0.1125160118574787</v>
       </c>
       <c r="T11">
-        <v>0.9636134806608279</v>
+        <v>0.9707992635143762</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.87150068082384</v>
+        <v>22.38435061274146</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1045339106717308</v>
+        <v>0.1041850830164448</v>
       </c>
       <c r="C12">
-        <v>45.10239166253933</v>
+        <v>44.8081383636091</v>
       </c>
       <c r="D12">
-        <v>40.46239166253932</v>
+        <v>40.7041383636091</v>
       </c>
       <c r="E12">
-        <v>-13.74</v>
+        <v>-13.204</v>
       </c>
       <c r="F12">
-        <v>5.36</v>
+        <v>5.896</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -2271,28 +2271,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M12">
-        <v>0.269608</v>
+        <v>0.2965688</v>
       </c>
       <c r="N12">
-        <v>5.765391999999999</v>
+        <v>5.738431199999999</v>
       </c>
       <c r="O12">
-        <v>2.0178872</v>
+        <v>2.00845092</v>
       </c>
       <c r="P12">
-        <v>3.7475048</v>
+        <v>3.729980279999999</v>
       </c>
       <c r="Q12">
-        <v>9.787504800000001</v>
+        <v>9.769980279999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1125160118574787</v>
+        <v>0.1130209359735334</v>
       </c>
       <c r="T12">
-        <v>0.9707992635143762</v>
+        <v>0.9781465246342965</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.38435061274146</v>
+        <v>20.34940964794678</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1041850830164448</v>
+        <v>0.1038362553611587</v>
       </c>
       <c r="C13">
-        <v>44.8081383636091</v>
+        <v>44.51679110795759</v>
       </c>
       <c r="D13">
-        <v>40.7041383636091</v>
+        <v>40.94879110795759</v>
       </c>
       <c r="E13">
-        <v>-13.204</v>
+        <v>-12.668</v>
       </c>
       <c r="F13">
-        <v>5.896</v>
+        <v>6.431999999999999</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -2353,28 +2353,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M13">
-        <v>0.2965688</v>
+        <v>0.3235296</v>
       </c>
       <c r="N13">
-        <v>5.738431199999999</v>
+        <v>5.7114704</v>
       </c>
       <c r="O13">
-        <v>2.00845092</v>
+        <v>1.99901464</v>
       </c>
       <c r="P13">
-        <v>3.729980279999999</v>
+        <v>3.71245576</v>
       </c>
       <c r="Q13">
-        <v>9.769980279999999</v>
+        <v>9.75245576</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1130209359735334</v>
+        <v>0.1135373356376803</v>
       </c>
       <c r="T13">
-        <v>0.9781465246342965</v>
+        <v>0.9856607689614875</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.34940964794678</v>
+        <v>18.65362551061789</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1038362553611587</v>
+        <v>0.1034874277058726</v>
       </c>
       <c r="C14">
-        <v>44.51679110795759</v>
+        <v>44.22840261287366</v>
       </c>
       <c r="D14">
-        <v>40.94879110795759</v>
+        <v>41.19640261287366</v>
       </c>
       <c r="E14">
-        <v>-12.668</v>
+        <v>-12.132</v>
       </c>
       <c r="F14">
-        <v>6.431999999999999</v>
+        <v>6.968000000000001</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -2435,28 +2435,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M14">
-        <v>0.3235296</v>
+        <v>0.3504904</v>
       </c>
       <c r="N14">
-        <v>5.7114704</v>
+        <v>5.684509599999999</v>
       </c>
       <c r="O14">
-        <v>1.99901464</v>
+        <v>1.98957836</v>
       </c>
       <c r="P14">
-        <v>3.71245576</v>
+        <v>3.69493124</v>
       </c>
       <c r="Q14">
-        <v>9.75245576</v>
+        <v>9.73493124</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1135373356376803</v>
+        <v>0.1140656065584743</v>
       </c>
       <c r="T14">
-        <v>0.9856607689614875</v>
+        <v>0.9933477545375795</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.65362551061789</v>
+        <v>17.21873124057035</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1034874277058726</v>
+        <v>0.1031386000505866</v>
       </c>
       <c r="C15">
-        <v>44.22840261287366</v>
+        <v>43.9430268784991</v>
       </c>
       <c r="D15">
-        <v>41.19640261287366</v>
+        <v>41.4470268784991</v>
       </c>
       <c r="E15">
-        <v>-12.132</v>
+        <v>-11.596</v>
       </c>
       <c r="F15">
-        <v>6.968000000000001</v>
+        <v>7.504000000000001</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -2517,28 +2517,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M15">
-        <v>0.3504904</v>
+        <v>0.3774512</v>
       </c>
       <c r="N15">
-        <v>5.684509599999999</v>
+        <v>5.657548799999999</v>
       </c>
       <c r="O15">
-        <v>1.98957836</v>
+        <v>1.98014208</v>
       </c>
       <c r="P15">
-        <v>3.69493124</v>
+        <v>3.67740672</v>
       </c>
       <c r="Q15">
-        <v>9.73493124</v>
+        <v>9.71740672</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1140656065584743</v>
+        <v>0.1146061628495192</v>
       </c>
       <c r="T15">
-        <v>0.9933477545375795</v>
+        <v>1.001213507220092</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.21873124057035</v>
+        <v>15.9888218662439</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1031386000505866</v>
+        <v>0.1027897723953005</v>
       </c>
       <c r="C16">
-        <v>43.9430268784991</v>
+        <v>43.66071922708968</v>
       </c>
       <c r="D16">
-        <v>41.4470268784991</v>
+        <v>41.70071922708968</v>
       </c>
       <c r="E16">
-        <v>-11.596</v>
+        <v>-11.06</v>
       </c>
       <c r="F16">
-        <v>7.504000000000001</v>
+        <v>8.040000000000001</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -2599,28 +2599,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M16">
-        <v>0.3774512</v>
+        <v>0.404412</v>
       </c>
       <c r="N16">
-        <v>5.657548799999999</v>
+        <v>5.630587999999999</v>
       </c>
       <c r="O16">
-        <v>1.98014208</v>
+        <v>1.9707058</v>
       </c>
       <c r="P16">
-        <v>3.67740672</v>
+        <v>3.6598822</v>
       </c>
       <c r="Q16">
-        <v>9.71740672</v>
+        <v>9.699882199999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1146061628495192</v>
+        <v>0.1151594381121182</v>
       </c>
       <c r="T16">
-        <v>1.001213507220092</v>
+        <v>1.009264336436311</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.9888218662439</v>
+        <v>14.92290040849431</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1027897723953005</v>
+        <v>0.1024409447400144</v>
       </c>
       <c r="C17">
-        <v>43.66071922708968</v>
+        <v>43.38153634372671</v>
       </c>
       <c r="D17">
-        <v>41.70071922708968</v>
+        <v>41.95753634372671</v>
       </c>
       <c r="E17">
-        <v>-11.06</v>
+        <v>-10.524</v>
       </c>
       <c r="F17">
-        <v>8.039999999999999</v>
+        <v>8.576000000000001</v>
       </c>
       <c r="G17">
         <v>10</v>
@@ -2681,28 +2681,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M17">
-        <v>0.4044119999999999</v>
+        <v>0.4313728</v>
       </c>
       <c r="N17">
-        <v>5.630587999999999</v>
+        <v>5.603627199999999</v>
       </c>
       <c r="O17">
-        <v>1.9707058</v>
+        <v>1.96126952</v>
       </c>
       <c r="P17">
-        <v>3.6598822</v>
+        <v>3.642357679999999</v>
       </c>
       <c r="Q17">
-        <v>9.699882199999999</v>
+        <v>9.682357679999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1151594381121182</v>
+        <v>0.1157258865952553</v>
       </c>
       <c r="T17">
-        <v>1.009264336436311</v>
+        <v>1.01750685206244</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.92290040849431</v>
+        <v>13.99021913296341</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1024409447400144</v>
+        <v>0.1020921170847283</v>
       </c>
       <c r="C18">
-        <v>43.38153634372671</v>
+        <v>43.1055363185426</v>
       </c>
       <c r="D18">
-        <v>41.95753634372671</v>
+        <v>42.2175363185426</v>
       </c>
       <c r="E18">
-        <v>-10.524</v>
+        <v>-9.988000000000001</v>
       </c>
       <c r="F18">
-        <v>8.576000000000001</v>
+        <v>9.112</v>
       </c>
       <c r="G18">
         <v>10</v>
@@ -2763,28 +2763,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M18">
-        <v>0.4313728</v>
+        <v>0.4583336</v>
       </c>
       <c r="N18">
-        <v>5.603627199999999</v>
+        <v>5.576666399999999</v>
       </c>
       <c r="O18">
-        <v>1.96126952</v>
+        <v>1.951833239999999</v>
       </c>
       <c r="P18">
-        <v>3.642357679999999</v>
+        <v>3.62483316</v>
       </c>
       <c r="Q18">
-        <v>9.682357679999999</v>
+        <v>9.664833160000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1157258865952553</v>
+        <v>0.1163059844394317</v>
       </c>
       <c r="T18">
-        <v>1.01750685206244</v>
+        <v>1.025947982522934</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.99021913296341</v>
+        <v>13.1672650663185</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1020921170847283</v>
+        <v>0.1019187894294423</v>
       </c>
       <c r="C19">
-        <v>43.1055363185426</v>
+        <v>42.69992877098936</v>
       </c>
       <c r="D19">
-        <v>42.2175363185426</v>
+        <v>42.34792877098936</v>
       </c>
       <c r="E19">
-        <v>-9.988000000000001</v>
+        <v>-9.452</v>
       </c>
       <c r="F19">
-        <v>9.112</v>
+        <v>9.648000000000001</v>
       </c>
       <c r="G19">
         <v>10</v>
@@ -2845,45 +2845,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M19">
-        <v>0.4583336</v>
+        <v>0.4997664000000001</v>
       </c>
       <c r="N19">
-        <v>5.576666399999999</v>
+        <v>5.535233599999999</v>
       </c>
       <c r="O19">
-        <v>1.951833239999999</v>
+        <v>1.93733176</v>
       </c>
       <c r="P19">
-        <v>3.62483316</v>
+        <v>3.59790184</v>
       </c>
       <c r="Q19">
-        <v>9.664833160000001</v>
+        <v>9.63790184</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1163059844394317</v>
+        <v>0.1169002310115149</v>
       </c>
       <c r="T19">
-        <v>1.025947982522934</v>
+        <v>1.034594994214171</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.1672650663185</v>
+        <v>12.07564173982084</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1019187894294423</v>
+        <v>0.1015797117741562</v>
       </c>
       <c r="C20">
-        <v>42.69992877098935</v>
+        <v>42.42135635419426</v>
       </c>
       <c r="D20">
-        <v>42.34792877098935</v>
+        <v>42.60535635419426</v>
       </c>
       <c r="E20">
-        <v>-9.452000000000002</v>
+        <v>-8.916</v>
       </c>
       <c r="F20">
-        <v>9.648</v>
+        <v>10.184</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2927,28 +2927,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M20">
-        <v>0.4997664</v>
+        <v>0.5275312000000001</v>
       </c>
       <c r="N20">
-        <v>5.535233599999999</v>
+        <v>5.507468799999999</v>
       </c>
       <c r="O20">
-        <v>1.93733176</v>
+        <v>1.927614079999999</v>
       </c>
       <c r="P20">
-        <v>3.59790184</v>
+        <v>3.579854719999999</v>
       </c>
       <c r="Q20">
-        <v>9.63790184</v>
+        <v>9.619854719999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1169002310115149</v>
+        <v>0.1175091503384645</v>
       </c>
       <c r="T20">
-        <v>1.034594994214171</v>
+        <v>1.04345551236692</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.07564173982084</v>
+        <v>11.44008164825132</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1015797117741562</v>
+        <v>0.1012406341188701</v>
       </c>
       <c r="C21">
-        <v>42.42135635419426</v>
+        <v>42.14593281701455</v>
       </c>
       <c r="D21">
-        <v>42.60535635419426</v>
+        <v>42.86593281701455</v>
       </c>
       <c r="E21">
-        <v>-8.916</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="F21">
-        <v>10.184</v>
+        <v>10.72</v>
       </c>
       <c r="G21">
         <v>10</v>
@@ -3009,28 +3009,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M21">
-        <v>0.5275312000000001</v>
+        <v>0.555296</v>
       </c>
       <c r="N21">
-        <v>5.507468799999999</v>
+        <v>5.479703999999999</v>
       </c>
       <c r="O21">
-        <v>1.927614079999999</v>
+        <v>1.9178964</v>
       </c>
       <c r="P21">
-        <v>3.579854719999999</v>
+        <v>3.561807599999999</v>
       </c>
       <c r="Q21">
-        <v>9.619854719999999</v>
+        <v>9.601807599999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1175091503384645</v>
+        <v>0.1181332926485877</v>
       </c>
       <c r="T21">
-        <v>1.04345551236692</v>
+        <v>1.052537543473488</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.44008164825132</v>
+        <v>10.86807756583876</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1012406341188701</v>
+        <v>0.1009015564635841</v>
       </c>
       <c r="C22">
-        <v>42.14593281701455</v>
+        <v>41.8737162910957</v>
       </c>
       <c r="D22">
-        <v>42.86593281701455</v>
+        <v>43.1297162910957</v>
       </c>
       <c r="E22">
-        <v>-8.380000000000001</v>
+        <v>-7.843999999999999</v>
       </c>
       <c r="F22">
-        <v>10.72</v>
+        <v>11.256</v>
       </c>
       <c r="G22">
         <v>10</v>
@@ -3091,28 +3091,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M22">
-        <v>0.555296</v>
+        <v>0.5830608</v>
       </c>
       <c r="N22">
-        <v>5.479703999999999</v>
+        <v>5.451939199999999</v>
       </c>
       <c r="O22">
-        <v>1.9178964</v>
+        <v>1.90817872</v>
       </c>
       <c r="P22">
-        <v>3.561807599999999</v>
+        <v>3.54376048</v>
       </c>
       <c r="Q22">
-        <v>9.601807599999999</v>
+        <v>9.583760479999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1181332926485877</v>
+        <v>0.1187732360298532</v>
       </c>
       <c r="T22">
-        <v>1.052537543473488</v>
+        <v>1.061849499418197</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.86807756583876</v>
+        <v>10.35055006270358</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1009015564635841</v>
+        <v>0.100562478808298</v>
       </c>
       <c r="C23">
-        <v>41.8737162910957</v>
+        <v>41.60476634783861</v>
       </c>
       <c r="D23">
-        <v>43.1297162910957</v>
+        <v>43.39676634783861</v>
       </c>
       <c r="E23">
-        <v>-7.844000000000001</v>
+        <v>-7.308000000000002</v>
       </c>
       <c r="F23">
-        <v>11.256</v>
+        <v>11.792</v>
       </c>
       <c r="G23">
         <v>10</v>
@@ -3173,28 +3173,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M23">
-        <v>0.5830608</v>
+        <v>0.6108256</v>
       </c>
       <c r="N23">
-        <v>5.451939199999999</v>
+        <v>5.424174399999999</v>
       </c>
       <c r="O23">
-        <v>1.90817872</v>
+        <v>1.898461039999999</v>
       </c>
       <c r="P23">
-        <v>3.54376048</v>
+        <v>3.52571336</v>
       </c>
       <c r="Q23">
-        <v>9.583760479999999</v>
+        <v>9.56571336</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1187732360298532</v>
+        <v>0.1194295882157667</v>
       </c>
       <c r="T23">
-        <v>1.061849499418197</v>
+        <v>1.071400223464053</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.35055006270358</v>
+        <v>9.880070514398872</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.100562478808298</v>
+        <v>0.1004775511530119</v>
       </c>
       <c r="C24">
-        <v>41.60476634783861</v>
+        <v>41.13617217591979</v>
       </c>
       <c r="D24">
-        <v>43.39676634783861</v>
+        <v>43.46417217591979</v>
       </c>
       <c r="E24">
-        <v>-7.308000000000002</v>
+        <v>-6.772</v>
       </c>
       <c r="F24">
-        <v>11.792</v>
+        <v>12.328</v>
       </c>
       <c r="G24">
         <v>10</v>
@@ -3255,45 +3255,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M24">
-        <v>0.6108256</v>
+        <v>0.659548</v>
       </c>
       <c r="N24">
-        <v>5.424174399999999</v>
+        <v>5.375451999999999</v>
       </c>
       <c r="O24">
-        <v>1.898461039999999</v>
+        <v>1.8814082</v>
       </c>
       <c r="P24">
-        <v>3.52571336</v>
+        <v>3.4940438</v>
       </c>
       <c r="Q24">
-        <v>9.56571336</v>
+        <v>9.534043799999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1194295882157667</v>
+        <v>0.1201029885104051</v>
       </c>
       <c r="T24">
-        <v>1.071400223464053</v>
+        <v>1.081199018264346</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.880070514398872</v>
+        <v>9.15020589858509</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1004775511530119</v>
+        <v>0.1001495234977259</v>
       </c>
       <c r="C25">
-        <v>41.13617217591979</v>
+        <v>40.86250107174558</v>
       </c>
       <c r="D25">
-        <v>43.46417217591979</v>
+        <v>43.72650107174558</v>
       </c>
       <c r="E25">
-        <v>-6.772</v>
+        <v>-6.236000000000001</v>
       </c>
       <c r="F25">
-        <v>12.328</v>
+        <v>12.864</v>
       </c>
       <c r="G25">
         <v>10</v>
@@ -3337,28 +3337,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M25">
-        <v>0.659548</v>
+        <v>0.6882240000000001</v>
       </c>
       <c r="N25">
-        <v>5.375451999999999</v>
+        <v>5.346775999999999</v>
       </c>
       <c r="O25">
-        <v>1.8814082</v>
+        <v>1.8713716</v>
       </c>
       <c r="P25">
-        <v>3.4940438</v>
+        <v>3.4754044</v>
       </c>
       <c r="Q25">
-        <v>9.534043799999999</v>
+        <v>9.5154044</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1201029885104051</v>
+        <v>0.1207941098654287</v>
       </c>
       <c r="T25">
-        <v>1.081199018264346</v>
+        <v>1.091255676085699</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.15020589858509</v>
+        <v>8.768947319477377</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1001495234977259</v>
+        <v>0.09982149584243977</v>
       </c>
       <c r="C26">
-        <v>40.86250107174558</v>
+        <v>40.59201577837763</v>
       </c>
       <c r="D26">
-        <v>43.72650107174558</v>
+        <v>43.99201577837763</v>
       </c>
       <c r="E26">
-        <v>-6.236000000000002</v>
+        <v>-5.700000000000001</v>
       </c>
       <c r="F26">
-        <v>12.864</v>
+        <v>13.4</v>
       </c>
       <c r="G26">
         <v>10</v>
@@ -3419,28 +3419,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M26">
-        <v>0.6882239999999999</v>
+        <v>0.7169</v>
       </c>
       <c r="N26">
-        <v>5.346775999999999</v>
+        <v>5.318099999999999</v>
       </c>
       <c r="O26">
-        <v>1.8713716</v>
+        <v>1.861335</v>
       </c>
       <c r="P26">
-        <v>3.4754044</v>
+        <v>3.456765</v>
       </c>
       <c r="Q26">
-        <v>9.5154044</v>
+        <v>9.496765</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1207941098654287</v>
+        <v>0.121503661123253</v>
       </c>
       <c r="T26">
-        <v>1.091255676085699</v>
+        <v>1.101580511448955</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.76894731947738</v>
+        <v>8.418189426698284</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09982149584243977</v>
+        <v>0.09949346818715371</v>
       </c>
       <c r="C27">
-        <v>40.59201577837763</v>
+        <v>40.32477468470844</v>
       </c>
       <c r="D27">
-        <v>43.99201577837763</v>
+        <v>44.26077468470844</v>
       </c>
       <c r="E27">
-        <v>-5.700000000000001</v>
+        <v>-5.164</v>
       </c>
       <c r="F27">
-        <v>13.4</v>
+        <v>13.936</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -3501,28 +3501,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M27">
-        <v>0.7169</v>
+        <v>0.7455760000000001</v>
       </c>
       <c r="N27">
-        <v>5.318099999999999</v>
+        <v>5.289423999999999</v>
       </c>
       <c r="O27">
-        <v>1.861335</v>
+        <v>1.8512984</v>
       </c>
       <c r="P27">
-        <v>3.456765</v>
+        <v>3.4381256</v>
       </c>
       <c r="Q27">
-        <v>9.496765</v>
+        <v>9.4781256</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.121503661123253</v>
+        <v>0.1222323894420996</v>
       </c>
       <c r="T27">
-        <v>1.101580511448955</v>
+        <v>1.112184396416624</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.418189426698284</v>
+        <v>8.09441291028681</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09949346818715371</v>
+        <v>0.09916544053186764</v>
       </c>
       <c r="C28">
-        <v>40.32477468470844</v>
+        <v>40.06083761525429</v>
       </c>
       <c r="D28">
-        <v>44.26077468470844</v>
+        <v>44.53283761525429</v>
       </c>
       <c r="E28">
-        <v>-5.164</v>
+        <v>-4.628</v>
       </c>
       <c r="F28">
-        <v>13.936</v>
+        <v>14.472</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -3583,28 +3583,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M28">
-        <v>0.7455760000000001</v>
+        <v>0.7742520000000001</v>
       </c>
       <c r="N28">
-        <v>5.289423999999999</v>
+        <v>5.260748</v>
       </c>
       <c r="O28">
-        <v>1.8512984</v>
+        <v>1.8412618</v>
       </c>
       <c r="P28">
-        <v>3.4381256</v>
+        <v>3.4194862</v>
       </c>
       <c r="Q28">
-        <v>9.4781256</v>
+        <v>9.459486200000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1222323894420996</v>
+        <v>0.1229810829203666</v>
       </c>
       <c r="T28">
-        <v>1.112184396416624</v>
+        <v>1.123078798780667</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.09441291028681</v>
+        <v>7.794619839535447</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09916544053186764</v>
+        <v>0.09898301287658157</v>
       </c>
       <c r="C29">
-        <v>40.06083761525429</v>
+        <v>39.67759355573174</v>
       </c>
       <c r="D29">
-        <v>44.53283761525429</v>
+        <v>44.68559355573174</v>
       </c>
       <c r="E29">
-        <v>-4.628</v>
+        <v>-4.091999999999999</v>
       </c>
       <c r="F29">
-        <v>14.472</v>
+        <v>15.008</v>
       </c>
       <c r="G29">
         <v>10</v>
@@ -3665,45 +3665,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M29">
-        <v>0.7742520000000001</v>
+        <v>0.8149344000000002</v>
       </c>
       <c r="N29">
-        <v>5.260748</v>
+        <v>5.220065599999999</v>
       </c>
       <c r="O29">
-        <v>1.8412618</v>
+        <v>1.827022959999999</v>
       </c>
       <c r="P29">
-        <v>3.4194862</v>
+        <v>3.39304264</v>
       </c>
       <c r="Q29">
-        <v>9.459486200000001</v>
+        <v>9.43304264</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1229810829203666</v>
+        <v>0.1237505734396966</v>
       </c>
       <c r="T29">
-        <v>1.123078798780667</v>
+        <v>1.1342758234326</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.794619839535447</v>
+        <v>7.405504050387366</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09898301287658157</v>
+        <v>0.09866018522129549</v>
       </c>
       <c r="C30">
-        <v>39.67759355573174</v>
+        <v>39.41449735529791</v>
       </c>
       <c r="D30">
-        <v>44.68559355573174</v>
+        <v>44.95849735529792</v>
       </c>
       <c r="E30">
-        <v>-4.091999999999999</v>
+        <v>-3.555999999999999</v>
       </c>
       <c r="F30">
-        <v>15.008</v>
+        <v>15.544</v>
       </c>
       <c r="G30">
         <v>10</v>
@@ -3747,28 +3747,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M30">
-        <v>0.8149344000000002</v>
+        <v>0.8440392000000001</v>
       </c>
       <c r="N30">
-        <v>5.220065599999999</v>
+        <v>5.190960799999999</v>
       </c>
       <c r="O30">
-        <v>1.827022959999999</v>
+        <v>1.81683628</v>
       </c>
       <c r="P30">
-        <v>3.39304264</v>
+        <v>3.37412452</v>
       </c>
       <c r="Q30">
-        <v>9.43304264</v>
+        <v>9.41412452</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1237505734396966</v>
+        <v>0.1245417397483035</v>
       </c>
       <c r="T30">
-        <v>1.1342758234326</v>
+        <v>1.145788257229658</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.405504050387366</v>
+        <v>7.15014184175332</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09866018522129549</v>
+        <v>0.09833735756600942</v>
       </c>
       <c r="C31">
-        <v>39.41449735529792</v>
+        <v>39.1547549928877</v>
       </c>
       <c r="D31">
-        <v>44.95849735529792</v>
+        <v>45.2347549928877</v>
       </c>
       <c r="E31">
-        <v>-3.556000000000003</v>
+        <v>-3.020000000000003</v>
       </c>
       <c r="F31">
-        <v>15.544</v>
+        <v>16.08</v>
       </c>
       <c r="G31">
         <v>10</v>
@@ -3829,28 +3829,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M31">
-        <v>0.8440392</v>
+        <v>0.8731439999999999</v>
       </c>
       <c r="N31">
-        <v>5.190960799999999</v>
+        <v>5.161855999999999</v>
       </c>
       <c r="O31">
-        <v>1.81683628</v>
+        <v>1.8066496</v>
       </c>
       <c r="P31">
-        <v>3.37412452</v>
+        <v>3.3552064</v>
       </c>
       <c r="Q31">
-        <v>9.41412452</v>
+        <v>9.395206399999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1245417397483035</v>
+        <v>0.1253555108085849</v>
       </c>
       <c r="T31">
-        <v>1.145788257229658</v>
+        <v>1.157629617706632</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.150141841753321</v>
+        <v>6.911803780361544</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09833735756600942</v>
+        <v>0.09801452991072335</v>
       </c>
       <c r="C32">
-        <v>39.1547549928877</v>
+        <v>38.89842867599396</v>
       </c>
       <c r="D32">
-        <v>45.2347549928877</v>
+        <v>45.51442867599396</v>
       </c>
       <c r="E32">
-        <v>-3.020000000000003</v>
+        <v>-2.484000000000002</v>
       </c>
       <c r="F32">
-        <v>16.08</v>
+        <v>16.616</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3911,28 +3911,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M32">
-        <v>0.8731439999999999</v>
+        <v>0.9022488</v>
       </c>
       <c r="N32">
-        <v>5.161855999999999</v>
+        <v>5.1327512</v>
       </c>
       <c r="O32">
-        <v>1.8066496</v>
+        <v>1.79646292</v>
       </c>
       <c r="P32">
-        <v>3.3552064</v>
+        <v>3.33628828</v>
       </c>
       <c r="Q32">
-        <v>9.395206399999999</v>
+        <v>9.376288280000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1253555108085849</v>
+        <v>0.1261928694358309</v>
       </c>
       <c r="T32">
-        <v>1.157629617706632</v>
+        <v>1.169814206023518</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.911803780361544</v>
+        <v>6.688842368091817</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09801452991072335</v>
+        <v>0.09769170225543727</v>
       </c>
       <c r="C33">
-        <v>38.89842867599396</v>
+        <v>38.64558216012575</v>
       </c>
       <c r="D33">
-        <v>45.51442867599396</v>
+        <v>45.79758216012575</v>
       </c>
       <c r="E33">
-        <v>-2.484000000000002</v>
+        <v>-1.948</v>
       </c>
       <c r="F33">
-        <v>16.616</v>
+        <v>17.152</v>
       </c>
       <c r="G33">
         <v>10</v>
@@ -3993,28 +3993,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M33">
-        <v>0.9022488</v>
+        <v>0.9313536000000001</v>
       </c>
       <c r="N33">
-        <v>5.1327512</v>
+        <v>5.103646399999999</v>
       </c>
       <c r="O33">
-        <v>1.79646292</v>
+        <v>1.786276239999999</v>
       </c>
       <c r="P33">
-        <v>3.33628828</v>
+        <v>3.317370159999999</v>
       </c>
       <c r="Q33">
-        <v>9.376288280000001</v>
+        <v>9.357370159999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1261928694358309</v>
+        <v>0.127054856257996</v>
       </c>
       <c r="T33">
-        <v>1.169814206023518</v>
+        <v>1.182357164585019</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.688842368091817</v>
+        <v>6.479816044088945</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09769170225543727</v>
+        <v>0.09736887460015121</v>
       </c>
       <c r="C34">
-        <v>38.64558216012575</v>
+        <v>38.39628079726221</v>
       </c>
       <c r="D34">
-        <v>45.79758216012575</v>
+        <v>46.08428079726221</v>
       </c>
       <c r="E34">
-        <v>-1.948</v>
+        <v>-1.411999999999999</v>
       </c>
       <c r="F34">
-        <v>17.152</v>
+        <v>17.688</v>
       </c>
       <c r="G34">
         <v>10</v>
@@ -4075,28 +4075,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M34">
-        <v>0.9313536000000001</v>
+        <v>0.9604584000000002</v>
       </c>
       <c r="N34">
-        <v>5.103646399999999</v>
+        <v>5.074541599999999</v>
       </c>
       <c r="O34">
-        <v>1.786276239999999</v>
+        <v>1.77608956</v>
       </c>
       <c r="P34">
-        <v>3.317370159999999</v>
+        <v>3.298452039999999</v>
       </c>
       <c r="Q34">
-        <v>9.357370159999999</v>
+        <v>9.33845204</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.127054856257996</v>
+        <v>0.1279425740300764</v>
       </c>
       <c r="T34">
-        <v>1.182357164585019</v>
+        <v>1.195274539819997</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.479816044088945</v>
+        <v>6.283457982146857</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09736887460015121</v>
+        <v>0.09726704694486515</v>
       </c>
       <c r="C35">
-        <v>38.39628079726221</v>
+        <v>37.95145863896268</v>
       </c>
       <c r="D35">
-        <v>46.08428079726221</v>
+        <v>46.17545863896267</v>
       </c>
       <c r="E35">
-        <v>-1.411999999999999</v>
+        <v>-0.8760000000000012</v>
       </c>
       <c r="F35">
-        <v>17.688</v>
+        <v>18.224</v>
       </c>
       <c r="G35">
         <v>10</v>
@@ -4157,45 +4157,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M35">
-        <v>0.9604584000000002</v>
+        <v>1.0077872</v>
       </c>
       <c r="N35">
-        <v>5.074541599999999</v>
+        <v>5.027212799999999</v>
       </c>
       <c r="O35">
-        <v>1.77608956</v>
+        <v>1.75952448</v>
       </c>
       <c r="P35">
-        <v>3.298452039999999</v>
+        <v>3.26768832</v>
       </c>
       <c r="Q35">
-        <v>9.33845204</v>
+        <v>9.30768832</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1279425740300764</v>
+        <v>0.1288571923407048</v>
       </c>
       <c r="T35">
-        <v>1.195274539819997</v>
+        <v>1.208583350668157</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.35</v>
       </c>
       <c r="W35">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.283457982146857</v>
+        <v>5.988367385495667</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09726704694486515</v>
+        <v>0.09695071928957907</v>
       </c>
       <c r="C36">
-        <v>37.95145863896268</v>
+        <v>37.7010181533916</v>
       </c>
       <c r="D36">
-        <v>46.17545863896267</v>
+        <v>46.46101815339161</v>
       </c>
       <c r="E36">
-        <v>-0.8760000000000012</v>
+        <v>-0.3399999999999999</v>
       </c>
       <c r="F36">
-        <v>18.224</v>
+        <v>18.76</v>
       </c>
       <c r="G36">
         <v>10</v>
@@ -4239,28 +4239,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M36">
-        <v>1.0077872</v>
+        <v>1.037428</v>
       </c>
       <c r="N36">
-        <v>5.027212799999999</v>
+        <v>4.997571999999999</v>
       </c>
       <c r="O36">
-        <v>1.75952448</v>
+        <v>1.7491502</v>
       </c>
       <c r="P36">
-        <v>3.26768832</v>
+        <v>3.248421799999999</v>
       </c>
       <c r="Q36">
-        <v>9.30768832</v>
+        <v>9.288421799999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1288571923407048</v>
+        <v>0.1297999527531986</v>
       </c>
       <c r="T36">
-        <v>1.208583350668157</v>
+        <v>1.222301663388567</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.988367385495667</v>
+        <v>5.817271174481506</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09695071928957907</v>
+        <v>0.09663439163429299</v>
       </c>
       <c r="C37">
-        <v>37.7010181533916</v>
+        <v>37.45413157566676</v>
       </c>
       <c r="D37">
-        <v>46.46101815339161</v>
+        <v>46.75013157566677</v>
       </c>
       <c r="E37">
-        <v>-0.3399999999999999</v>
+        <v>0.1960000000000015</v>
       </c>
       <c r="F37">
-        <v>18.76</v>
+        <v>19.296</v>
       </c>
       <c r="G37">
         <v>10</v>
@@ -4321,28 +4321,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M37">
-        <v>1.037428</v>
+        <v>1.0670688</v>
       </c>
       <c r="N37">
-        <v>4.997571999999999</v>
+        <v>4.967931199999999</v>
       </c>
       <c r="O37">
-        <v>1.7491502</v>
+        <v>1.738775919999999</v>
       </c>
       <c r="P37">
-        <v>3.248421799999999</v>
+        <v>3.22915528</v>
       </c>
       <c r="Q37">
-        <v>9.288421799999998</v>
+        <v>9.26915528</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1297999527531986</v>
+        <v>0.1307721744285828</v>
       </c>
       <c r="T37">
-        <v>1.222301663388567</v>
+        <v>1.23644867338149</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.817271174481506</v>
+        <v>5.655680308523685</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09663439163429301</v>
+        <v>0.09631806397900694</v>
       </c>
       <c r="C38">
-        <v>37.45413157566675</v>
+        <v>37.21086566602681</v>
       </c>
       <c r="D38">
-        <v>46.75013157566675</v>
+        <v>47.04286566602681</v>
       </c>
       <c r="E38">
-        <v>0.195999999999998</v>
+        <v>0.7319999999999993</v>
       </c>
       <c r="F38">
-        <v>19.296</v>
+        <v>19.832</v>
       </c>
       <c r="G38">
         <v>10</v>
@@ -4403,28 +4403,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M38">
-        <v>1.0670688</v>
+        <v>1.0967096</v>
       </c>
       <c r="N38">
-        <v>4.967931199999999</v>
+        <v>4.9382904</v>
       </c>
       <c r="O38">
-        <v>1.738775919999999</v>
+        <v>1.72840164</v>
       </c>
       <c r="P38">
-        <v>3.22915528</v>
+        <v>3.20988876</v>
       </c>
       <c r="Q38">
-        <v>9.26915528</v>
+        <v>9.249888760000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1307721744285828</v>
+        <v>0.131775260284138</v>
       </c>
       <c r="T38">
-        <v>1.23644867338149</v>
+        <v>1.25104479480276</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.655680308523686</v>
+        <v>5.502824083968992</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09631806397900694</v>
+        <v>0.09600173632372087</v>
       </c>
       <c r="C39">
-        <v>37.21086566602681</v>
+        <v>36.97128886737014</v>
       </c>
       <c r="D39">
-        <v>47.04286566602681</v>
+        <v>47.33928886737014</v>
       </c>
       <c r="E39">
-        <v>0.7319999999999993</v>
+        <v>1.268000000000001</v>
       </c>
       <c r="F39">
-        <v>19.832</v>
+        <v>20.368</v>
       </c>
       <c r="G39">
         <v>10</v>
@@ -4485,28 +4485,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M39">
-        <v>1.0967096</v>
+        <v>1.1263504</v>
       </c>
       <c r="N39">
-        <v>4.9382904</v>
+        <v>4.908649599999999</v>
       </c>
       <c r="O39">
-        <v>1.72840164</v>
+        <v>1.718027359999999</v>
       </c>
       <c r="P39">
-        <v>3.20988876</v>
+        <v>3.190622239999999</v>
       </c>
       <c r="Q39">
-        <v>9.249888760000001</v>
+        <v>9.230622239999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.131775260284138</v>
+        <v>0.1328107037479369</v>
       </c>
       <c r="T39">
-        <v>1.25104479480276</v>
+        <v>1.266111758850523</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.502824083968992</v>
+        <v>5.358012923864544</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09600173632372087</v>
+        <v>0.09568540866843481</v>
       </c>
       <c r="C40">
-        <v>36.97128886737014</v>
+        <v>36.73547135860431</v>
       </c>
       <c r="D40">
-        <v>47.33928886737014</v>
+        <v>47.63947135860432</v>
       </c>
       <c r="E40">
-        <v>1.268000000000001</v>
+        <v>1.803999999999998</v>
       </c>
       <c r="F40">
-        <v>20.368</v>
+        <v>20.904</v>
       </c>
       <c r="G40">
         <v>10</v>
@@ -4567,28 +4567,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M40">
-        <v>1.1263504</v>
+        <v>1.1559912</v>
       </c>
       <c r="N40">
-        <v>4.908649599999999</v>
+        <v>4.879008799999999</v>
       </c>
       <c r="O40">
-        <v>1.718027359999999</v>
+        <v>1.70765308</v>
       </c>
       <c r="P40">
-        <v>3.190622239999999</v>
+        <v>3.17135572</v>
       </c>
       <c r="Q40">
-        <v>9.230622239999999</v>
+        <v>9.21135572</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1328107037479369</v>
+        <v>0.133880096177762</v>
       </c>
       <c r="T40">
-        <v>1.266111758850523</v>
+        <v>1.281672721719524</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.358012923864544</v>
+        <v>5.220627977098786</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09568540866843481</v>
+        <v>0.09536908101314871</v>
       </c>
       <c r="C41">
-        <v>36.73547135860431</v>
+        <v>36.50348511003817</v>
       </c>
       <c r="D41">
-        <v>47.63947135860432</v>
+        <v>47.94348511003817</v>
       </c>
       <c r="E41">
-        <v>1.803999999999998</v>
+        <v>2.34</v>
       </c>
       <c r="F41">
-        <v>20.904</v>
+        <v>21.44</v>
       </c>
       <c r="G41">
         <v>10</v>
@@ -4649,28 +4649,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M41">
-        <v>1.1559912</v>
+        <v>1.185632</v>
       </c>
       <c r="N41">
-        <v>4.879008799999999</v>
+        <v>4.849367999999999</v>
       </c>
       <c r="O41">
-        <v>1.70765308</v>
+        <v>1.6972788</v>
       </c>
       <c r="P41">
-        <v>3.17135572</v>
+        <v>3.1520892</v>
       </c>
       <c r="Q41">
-        <v>9.21135572</v>
+        <v>9.1920892</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.133880096177762</v>
+        <v>0.1349851350219145</v>
       </c>
       <c r="T41">
-        <v>1.281672721719524</v>
+        <v>1.297752383350824</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.220627977098786</v>
+        <v>5.090112277671317</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09536908101314871</v>
+        <v>0.09505275335786265</v>
       </c>
       <c r="C42">
-        <v>36.50348511003817</v>
+        <v>36.27540394090856</v>
       </c>
       <c r="D42">
-        <v>47.94348511003817</v>
+        <v>48.25140394090857</v>
       </c>
       <c r="E42">
-        <v>2.34</v>
+        <v>2.876000000000001</v>
       </c>
       <c r="F42">
-        <v>21.44</v>
+        <v>21.976</v>
       </c>
       <c r="G42">
         <v>10</v>
@@ -4731,28 +4731,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M42">
-        <v>1.185632</v>
+        <v>1.2152728</v>
       </c>
       <c r="N42">
-        <v>4.849367999999999</v>
+        <v>4.819727199999999</v>
       </c>
       <c r="O42">
-        <v>1.6972788</v>
+        <v>1.68690452</v>
       </c>
       <c r="P42">
-        <v>3.1520892</v>
+        <v>3.132822679999999</v>
       </c>
       <c r="Q42">
-        <v>9.1920892</v>
+        <v>9.172822679999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1349851350219145</v>
+        <v>0.1361276328099367</v>
       </c>
       <c r="T42">
-        <v>1.297752383350824</v>
+        <v>1.314377118257762</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.090112277671317</v>
+        <v>4.965963197728113</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09505275335786265</v>
+        <v>0.09473642570257659</v>
       </c>
       <c r="C43">
-        <v>36.27540394090856</v>
+        <v>36.05130357913825</v>
       </c>
       <c r="D43">
-        <v>48.25140394090857</v>
+        <v>48.56330357913826</v>
       </c>
       <c r="E43">
-        <v>2.876000000000001</v>
+        <v>3.412000000000003</v>
       </c>
       <c r="F43">
-        <v>21.976</v>
+        <v>22.512</v>
       </c>
       <c r="G43">
         <v>10</v>
@@ -4813,28 +4813,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M43">
-        <v>1.2152728</v>
+        <v>1.2449136</v>
       </c>
       <c r="N43">
-        <v>4.819727199999999</v>
+        <v>4.790086399999999</v>
       </c>
       <c r="O43">
-        <v>1.68690452</v>
+        <v>1.67653024</v>
       </c>
       <c r="P43">
-        <v>3.132822679999999</v>
+        <v>3.113556159999999</v>
       </c>
       <c r="Q43">
-        <v>9.172822679999999</v>
+        <v>9.153556159999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1361276328099367</v>
+        <v>0.1373095270734079</v>
       </c>
       <c r="T43">
-        <v>1.314377118257762</v>
+        <v>1.331575119885629</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.965963197728113</v>
+        <v>4.847725978734587</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09473642570257659</v>
+        <v>0.09442009804729053</v>
       </c>
       <c r="C44">
-        <v>36.05130357913826</v>
+        <v>35.83126172342649</v>
       </c>
       <c r="D44">
-        <v>48.56330357913826</v>
+        <v>48.8792617234265</v>
       </c>
       <c r="E44">
-        <v>3.411999999999999</v>
+        <v>3.948</v>
       </c>
       <c r="F44">
-        <v>22.512</v>
+        <v>23.048</v>
       </c>
       <c r="G44">
         <v>10</v>
@@ -4895,28 +4895,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M44">
-        <v>1.2449136</v>
+        <v>1.2745544</v>
       </c>
       <c r="N44">
-        <v>4.790086399999999</v>
+        <v>4.760445599999999</v>
       </c>
       <c r="O44">
-        <v>1.67653024</v>
+        <v>1.66615596</v>
       </c>
       <c r="P44">
-        <v>3.113556159999999</v>
+        <v>3.09428964</v>
       </c>
       <c r="Q44">
-        <v>9.153556159999999</v>
+        <v>9.134289639999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1373095270734079</v>
+        <v>0.138532891311036</v>
       </c>
       <c r="T44">
-        <v>1.331575119885629</v>
+        <v>1.349376560167105</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.847725978734587</v>
+        <v>4.734988165275643</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09442009804729053</v>
+        <v>0.09410377039200445</v>
       </c>
       <c r="C45">
-        <v>35.83126172342649</v>
+        <v>35.61535810777926</v>
       </c>
       <c r="D45">
-        <v>48.8792617234265</v>
+        <v>49.19935810777925</v>
       </c>
       <c r="E45">
-        <v>3.948</v>
+        <v>4.483999999999998</v>
       </c>
       <c r="F45">
-        <v>23.048</v>
+        <v>23.584</v>
       </c>
       <c r="G45">
         <v>10</v>
@@ -4977,28 +4977,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M45">
-        <v>1.2745544</v>
+        <v>1.3041952</v>
       </c>
       <c r="N45">
-        <v>4.760445599999999</v>
+        <v>4.7308048</v>
       </c>
       <c r="O45">
-        <v>1.66615596</v>
+        <v>1.65578168</v>
       </c>
       <c r="P45">
-        <v>3.09428964</v>
+        <v>3.07502312</v>
       </c>
       <c r="Q45">
-        <v>9.134289639999999</v>
+        <v>9.11502312</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.138532891311036</v>
+        <v>0.1397999471285793</v>
       </c>
       <c r="T45">
-        <v>1.349376560167105</v>
+        <v>1.36781376617292</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.734988165275643</v>
+        <v>4.627374797883016</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09410377039200445</v>
+        <v>0.09378744273671838</v>
       </c>
       <c r="C46">
-        <v>35.61535810777926</v>
+        <v>35.40367456859171</v>
       </c>
       <c r="D46">
-        <v>49.19935810777925</v>
+        <v>49.52367456859172</v>
       </c>
       <c r="E46">
-        <v>4.483999999999998</v>
+        <v>5.02</v>
       </c>
       <c r="F46">
-        <v>23.584</v>
+        <v>24.12</v>
       </c>
       <c r="G46">
         <v>10</v>
@@ -5059,28 +5059,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M46">
-        <v>1.3041952</v>
+        <v>1.333836</v>
       </c>
       <c r="N46">
-        <v>4.7308048</v>
+        <v>4.701163999999999</v>
       </c>
       <c r="O46">
-        <v>1.65578168</v>
+        <v>1.6454074</v>
       </c>
       <c r="P46">
-        <v>3.07502312</v>
+        <v>3.0557566</v>
       </c>
       <c r="Q46">
-        <v>9.11502312</v>
+        <v>9.0957566</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1397999471285793</v>
+        <v>0.1411130777031243</v>
       </c>
       <c r="T46">
-        <v>1.36781376617292</v>
+        <v>1.386921416033492</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.627374797883016</v>
+        <v>4.524544246818949</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09378744273671838</v>
+        <v>0.09421861508143231</v>
       </c>
       <c r="C47">
-        <v>35.40367456859171</v>
+        <v>34.42666156467418</v>
       </c>
       <c r="D47">
-        <v>49.52367456859172</v>
+        <v>49.08266156467418</v>
       </c>
       <c r="E47">
-        <v>5.02</v>
+        <v>5.556000000000001</v>
       </c>
       <c r="F47">
-        <v>24.12</v>
+        <v>24.656</v>
       </c>
       <c r="G47">
         <v>10</v>
@@ -5141,45 +5141,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M47">
-        <v>1.333836</v>
+        <v>1.4251168</v>
       </c>
       <c r="N47">
-        <v>4.701163999999999</v>
+        <v>4.609883199999999</v>
       </c>
       <c r="O47">
-        <v>1.6454074</v>
+        <v>1.613459119999999</v>
       </c>
       <c r="P47">
-        <v>3.0557566</v>
+        <v>2.996424079999999</v>
       </c>
       <c r="Q47">
-        <v>9.0957566</v>
+        <v>9.03642408</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1411130777031243</v>
+        <v>0.1424748427433931</v>
       </c>
       <c r="T47">
-        <v>1.386921416033492</v>
+        <v>1.40673675662964</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.524544246818949</v>
+        <v>4.234740619154863</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09421861508143231</v>
+        <v>0.09391853742614623</v>
       </c>
       <c r="C48">
-        <v>34.42666156467418</v>
+        <v>34.19675170758705</v>
       </c>
       <c r="D48">
-        <v>49.08266156467418</v>
+        <v>49.38875170758706</v>
       </c>
       <c r="E48">
-        <v>5.556000000000001</v>
+        <v>6.092000000000002</v>
       </c>
       <c r="F48">
-        <v>24.656</v>
+        <v>25.192</v>
       </c>
       <c r="G48">
         <v>10</v>
@@ -5223,28 +5223,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M48">
-        <v>1.4251168</v>
+        <v>1.4560976</v>
       </c>
       <c r="N48">
-        <v>4.609883199999999</v>
+        <v>4.578902399999999</v>
       </c>
       <c r="O48">
-        <v>1.613459119999999</v>
+        <v>1.602615839999999</v>
       </c>
       <c r="P48">
-        <v>2.996424079999999</v>
+        <v>2.976286559999999</v>
       </c>
       <c r="Q48">
-        <v>9.03642408</v>
+        <v>9.016286559999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1424748427433931</v>
+        <v>0.1438879951436721</v>
       </c>
       <c r="T48">
-        <v>1.40673675662964</v>
+        <v>1.42729984592753</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.234740619154863</v>
+        <v>4.144639754917526</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09391853742614623</v>
+        <v>0.09361845977086017</v>
       </c>
       <c r="C49">
-        <v>34.19675170758705</v>
+        <v>33.97068349712892</v>
       </c>
       <c r="D49">
-        <v>49.38875170758706</v>
+        <v>49.69868349712892</v>
       </c>
       <c r="E49">
-        <v>6.092000000000002</v>
+        <v>6.628</v>
       </c>
       <c r="F49">
-        <v>25.192</v>
+        <v>25.728</v>
       </c>
       <c r="G49">
         <v>10</v>
@@ -5305,28 +5305,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M49">
-        <v>1.4560976</v>
+        <v>1.4870784</v>
       </c>
       <c r="N49">
-        <v>4.578902399999999</v>
+        <v>4.547921599999999</v>
       </c>
       <c r="O49">
-        <v>1.602615839999999</v>
+        <v>1.591772559999999</v>
       </c>
       <c r="P49">
-        <v>2.976286559999999</v>
+        <v>2.956149039999999</v>
       </c>
       <c r="Q49">
-        <v>9.016286559999999</v>
+        <v>8.996149039999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1438879951436721</v>
+        <v>0.1453554995593465</v>
       </c>
       <c r="T49">
-        <v>1.42729984592753</v>
+        <v>1.448653823275339</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.144639754917526</v>
+        <v>4.058293093356744</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09361845977086017</v>
+        <v>0.09443313211557409</v>
       </c>
       <c r="C50">
-        <v>33.97068349712892</v>
+        <v>32.60216169043994</v>
       </c>
       <c r="D50">
-        <v>49.69868349712892</v>
+        <v>48.86616169043995</v>
       </c>
       <c r="E50">
-        <v>6.627999999999997</v>
+        <v>7.163999999999998</v>
       </c>
       <c r="F50">
-        <v>25.728</v>
+        <v>26.264</v>
       </c>
       <c r="G50">
         <v>10</v>
@@ -5387,45 +5387,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M50">
-        <v>1.4870784</v>
+        <v>1.6099832</v>
       </c>
       <c r="N50">
-        <v>4.5479216</v>
+        <v>4.425016799999999</v>
       </c>
       <c r="O50">
-        <v>1.59177256</v>
+        <v>1.54875588</v>
       </c>
       <c r="P50">
-        <v>2.95614904</v>
+        <v>2.876260919999999</v>
       </c>
       <c r="Q50">
-        <v>8.996149039999999</v>
+        <v>8.916260919999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1453554995593465</v>
+        <v>0.1468805531677923</v>
       </c>
       <c r="T50">
-        <v>1.448653823275339</v>
+        <v>1.470845211499532</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.35</v>
       </c>
       <c r="W50">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.058293093356745</v>
+        <v>3.7484863196088</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09443313211557409</v>
+        <v>0.09415580446028801</v>
       </c>
       <c r="C51">
-        <v>32.60216169043994</v>
+        <v>32.34641631955215</v>
       </c>
       <c r="D51">
-        <v>48.86616169043995</v>
+        <v>49.14641631955215</v>
       </c>
       <c r="E51">
-        <v>7.163999999999998</v>
+        <v>7.699999999999999</v>
       </c>
       <c r="F51">
-        <v>26.264</v>
+        <v>26.8</v>
       </c>
       <c r="G51">
         <v>10</v>
@@ -5469,28 +5469,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M51">
-        <v>1.6099832</v>
+        <v>1.64284</v>
       </c>
       <c r="N51">
-        <v>4.425016799999999</v>
+        <v>4.392159999999999</v>
       </c>
       <c r="O51">
-        <v>1.54875588</v>
+        <v>1.537256</v>
       </c>
       <c r="P51">
-        <v>2.876260919999999</v>
+        <v>2.854903999999999</v>
       </c>
       <c r="Q51">
-        <v>8.916260919999999</v>
+        <v>8.894904</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1468805531677923</v>
+        <v>0.148466608920576</v>
       </c>
       <c r="T51">
-        <v>1.470845211499532</v>
+        <v>1.493924255252693</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.7484863196088</v>
+        <v>3.673516593216624</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09415580446028801</v>
+        <v>0.09387847680500194</v>
       </c>
       <c r="C52">
-        <v>32.34641631955215</v>
+        <v>32.09390409431867</v>
       </c>
       <c r="D52">
-        <v>49.14641631955215</v>
+        <v>49.42990409431868</v>
       </c>
       <c r="E52">
-        <v>7.699999999999999</v>
+        <v>8.236000000000001</v>
       </c>
       <c r="F52">
-        <v>26.8</v>
+        <v>27.336</v>
       </c>
       <c r="G52">
         <v>10</v>
@@ -5551,28 +5551,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M52">
-        <v>1.64284</v>
+        <v>1.6756968</v>
       </c>
       <c r="N52">
-        <v>4.392159999999999</v>
+        <v>4.359303199999999</v>
       </c>
       <c r="O52">
-        <v>1.537256</v>
+        <v>1.52575612</v>
       </c>
       <c r="P52">
-        <v>2.854903999999999</v>
+        <v>2.83354708</v>
       </c>
       <c r="Q52">
-        <v>8.894904</v>
+        <v>8.87354708</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.148466608920576</v>
+        <v>0.1501174016428611</v>
       </c>
       <c r="T52">
-        <v>1.493924255252693</v>
+        <v>1.517945300791697</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.673516593216624</v>
+        <v>3.60148685609473</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09387847680500194</v>
+        <v>0.09360114914971587</v>
       </c>
       <c r="C53">
-        <v>32.09390409431867</v>
+        <v>31.84468128790784</v>
       </c>
       <c r="D53">
-        <v>49.42990409431868</v>
+        <v>49.71668128790785</v>
       </c>
       <c r="E53">
-        <v>8.236000000000001</v>
+        <v>8.772000000000002</v>
       </c>
       <c r="F53">
-        <v>27.336</v>
+        <v>27.872</v>
       </c>
       <c r="G53">
         <v>10</v>
@@ -5633,28 +5633,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M53">
-        <v>1.6756968</v>
+        <v>1.7085536</v>
       </c>
       <c r="N53">
-        <v>4.359303199999999</v>
+        <v>4.326446399999999</v>
       </c>
       <c r="O53">
-        <v>1.52575612</v>
+        <v>1.51425624</v>
       </c>
       <c r="P53">
-        <v>2.83354708</v>
+        <v>2.812190159999999</v>
       </c>
       <c r="Q53">
-        <v>8.87354708</v>
+        <v>8.852190159999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1501174016428611</v>
+        <v>0.1518369773952414</v>
       </c>
       <c r="T53">
-        <v>1.517945300791697</v>
+        <v>1.54296722322816</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.60148685609473</v>
+        <v>3.532227493477523</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09360114914971587</v>
+        <v>0.0942884214944298</v>
       </c>
       <c r="C54">
-        <v>31.84468128790784</v>
+        <v>30.6039996532611</v>
       </c>
       <c r="D54">
-        <v>49.71668128790785</v>
+        <v>49.0119996532611</v>
       </c>
       <c r="E54">
-        <v>8.772000000000002</v>
+        <v>9.308</v>
       </c>
       <c r="F54">
-        <v>27.872</v>
+        <v>28.408</v>
       </c>
       <c r="G54">
         <v>10</v>
@@ -5715,45 +5715,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M54">
-        <v>1.7085536</v>
+        <v>1.8209528</v>
       </c>
       <c r="N54">
-        <v>4.326446399999999</v>
+        <v>4.2140472</v>
       </c>
       <c r="O54">
-        <v>1.51425624</v>
+        <v>1.47491652</v>
       </c>
       <c r="P54">
-        <v>2.812190159999999</v>
+        <v>2.73913068</v>
       </c>
       <c r="Q54">
-        <v>8.852190159999999</v>
+        <v>8.77913068</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1518369773952414</v>
+        <v>0.1536297265838932</v>
       </c>
       <c r="T54">
-        <v>1.54296722322816</v>
+        <v>1.569053908321494</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.35</v>
       </c>
       <c r="W54">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.532227493477523</v>
+        <v>3.314199028113194</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0942884214944298</v>
+        <v>0.09402929383914374</v>
       </c>
       <c r="C55">
-        <v>30.6039996532611</v>
+        <v>30.33133265152951</v>
       </c>
       <c r="D55">
-        <v>49.0119996532611</v>
+        <v>49.27533265152952</v>
       </c>
       <c r="E55">
-        <v>9.308</v>
+        <v>9.844000000000001</v>
       </c>
       <c r="F55">
-        <v>28.408</v>
+        <v>28.944</v>
       </c>
       <c r="G55">
         <v>10</v>
@@ -5797,28 +5797,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M55">
-        <v>1.8209528</v>
+        <v>1.8553104</v>
       </c>
       <c r="N55">
-        <v>4.2140472</v>
+        <v>4.179689599999999</v>
       </c>
       <c r="O55">
-        <v>1.47491652</v>
+        <v>1.46289136</v>
       </c>
       <c r="P55">
-        <v>2.73913068</v>
+        <v>2.716798239999999</v>
       </c>
       <c r="Q55">
-        <v>8.77913068</v>
+        <v>8.756798239999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1536297265838932</v>
+        <v>0.1555004213894429</v>
       </c>
       <c r="T55">
-        <v>1.569053908321494</v>
+        <v>1.596274797114538</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.314199028113194</v>
+        <v>3.252824972037023</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09402929383914374</v>
+        <v>0.09377016618385767</v>
       </c>
       <c r="C56">
-        <v>30.33133265152951</v>
+        <v>30.06151062065502</v>
       </c>
       <c r="D56">
-        <v>49.27533265152952</v>
+        <v>49.54151062065502</v>
       </c>
       <c r="E56">
-        <v>9.844000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="F56">
-        <v>28.944</v>
+        <v>29.48</v>
       </c>
       <c r="G56">
         <v>10</v>
@@ -5879,28 +5879,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M56">
-        <v>1.8553104</v>
+        <v>1.889668</v>
       </c>
       <c r="N56">
-        <v>4.179689599999999</v>
+        <v>4.145331999999999</v>
       </c>
       <c r="O56">
-        <v>1.46289136</v>
+        <v>1.450866199999999</v>
       </c>
       <c r="P56">
-        <v>2.716798239999999</v>
+        <v>2.6944658</v>
       </c>
       <c r="Q56">
-        <v>8.756798239999998</v>
+        <v>8.734465799999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1555004213894429</v>
+        <v>0.1574542581863504</v>
       </c>
       <c r="T56">
-        <v>1.596274797114538</v>
+        <v>1.624705503187272</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.252824972037023</v>
+        <v>3.193682699818168</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09377016618385767</v>
+        <v>0.09351103852857159</v>
       </c>
       <c r="C57">
-        <v>30.06151062065502</v>
+        <v>29.79457991535865</v>
       </c>
       <c r="D57">
-        <v>49.54151062065502</v>
+        <v>49.81057991535866</v>
       </c>
       <c r="E57">
-        <v>10.38</v>
+        <v>10.916</v>
       </c>
       <c r="F57">
-        <v>29.48</v>
+        <v>30.01600000000001</v>
       </c>
       <c r="G57">
         <v>10</v>
@@ -5961,28 +5961,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M57">
-        <v>1.889668</v>
+        <v>1.9240256</v>
       </c>
       <c r="N57">
-        <v>4.145331999999999</v>
+        <v>4.110974399999999</v>
       </c>
       <c r="O57">
-        <v>1.450866199999999</v>
+        <v>1.43884104</v>
       </c>
       <c r="P57">
-        <v>2.6944658</v>
+        <v>2.672133359999999</v>
       </c>
       <c r="Q57">
-        <v>8.734465799999999</v>
+        <v>8.712133359999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1574542581863504</v>
+        <v>0.1594969057467536</v>
       </c>
       <c r="T57">
-        <v>1.624705503187272</v>
+        <v>1.654428514081495</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.193682699818168</v>
+        <v>3.136652651607129</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09351103852857159</v>
+        <v>0.09325191087328552</v>
       </c>
       <c r="C58">
-        <v>29.79457991535865</v>
+        <v>29.53058790290574</v>
       </c>
       <c r="D58">
-        <v>49.81057991535866</v>
+        <v>50.08258790290574</v>
       </c>
       <c r="E58">
-        <v>10.916</v>
+        <v>11.452</v>
       </c>
       <c r="F58">
-        <v>30.01600000000001</v>
+        <v>30.552</v>
       </c>
       <c r="G58">
         <v>10</v>
@@ -6043,28 +6043,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M58">
-        <v>1.9240256</v>
+        <v>1.9583832</v>
       </c>
       <c r="N58">
-        <v>4.110974399999999</v>
+        <v>4.076616799999999</v>
       </c>
       <c r="O58">
-        <v>1.43884104</v>
+        <v>1.42681588</v>
       </c>
       <c r="P58">
-        <v>2.672133359999999</v>
+        <v>2.64980092</v>
       </c>
       <c r="Q58">
-        <v>8.712133359999999</v>
+        <v>8.68980092</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1594969057467536</v>
+        <v>0.1616345601704315</v>
       </c>
       <c r="T58">
-        <v>1.654428514081495</v>
+        <v>1.685533990598704</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.136652651607129</v>
+        <v>3.081623657719285</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09325191087328552</v>
+        <v>0.09299278321799946</v>
       </c>
       <c r="C59">
-        <v>29.53058790290574</v>
+        <v>29.26958299090446</v>
       </c>
       <c r="D59">
-        <v>50.08258790290574</v>
+        <v>50.35758299090447</v>
       </c>
       <c r="E59">
-        <v>11.452</v>
+        <v>11.988</v>
       </c>
       <c r="F59">
-        <v>30.552</v>
+        <v>31.088</v>
       </c>
       <c r="G59">
         <v>10</v>
@@ -6125,28 +6125,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M59">
-        <v>1.9583832</v>
+        <v>1.9927408</v>
       </c>
       <c r="N59">
-        <v>4.076616799999999</v>
+        <v>4.042259199999998</v>
       </c>
       <c r="O59">
-        <v>1.42681588</v>
+        <v>1.414790719999999</v>
       </c>
       <c r="P59">
-        <v>2.64980092</v>
+        <v>2.627468479999999</v>
       </c>
       <c r="Q59">
-        <v>8.68980092</v>
+        <v>8.66746848</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1616345601704315</v>
+        <v>0.1638740076619035</v>
       </c>
       <c r="T59">
-        <v>1.685533990598704</v>
+        <v>1.7181206802834</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.081623657719285</v>
+        <v>3.028492215344814</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09299278321799945</v>
+        <v>0.09572495556271339</v>
       </c>
       <c r="C60">
-        <v>29.26958299090448</v>
+        <v>25.97773485756848</v>
       </c>
       <c r="D60">
-        <v>50.35758299090448</v>
+        <v>47.60173485756848</v>
       </c>
       <c r="E60">
-        <v>11.988</v>
+        <v>12.524</v>
       </c>
       <c r="F60">
-        <v>31.088</v>
+        <v>31.624</v>
       </c>
       <c r="G60">
         <v>10</v>
@@ -6207,45 +6207,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M60">
-        <v>1.9927408</v>
+        <v>2.2737656</v>
       </c>
       <c r="N60">
-        <v>4.042259199999999</v>
+        <v>3.761234399999999</v>
       </c>
       <c r="O60">
-        <v>1.41479072</v>
+        <v>1.31643204</v>
       </c>
       <c r="P60">
-        <v>2.62746848</v>
+        <v>2.44480236</v>
       </c>
       <c r="Q60">
-        <v>8.66746848</v>
+        <v>8.48480236</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1638740076619034</v>
+        <v>0.1662226964944229</v>
       </c>
       <c r="T60">
-        <v>1.7181206802834</v>
+        <v>1.752296964586861</v>
       </c>
       <c r="U60">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.35</v>
       </c>
       <c r="W60">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.028492215344815</v>
+        <v>2.654187397328907</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09572495556271339</v>
+        <v>0.09551652790742732</v>
       </c>
       <c r="C61">
-        <v>25.97773485756848</v>
+        <v>25.64129662106063</v>
       </c>
       <c r="D61">
-        <v>47.60173485756848</v>
+        <v>47.80129662106062</v>
       </c>
       <c r="E61">
-        <v>12.524</v>
+        <v>13.06</v>
       </c>
       <c r="F61">
-        <v>31.624</v>
+        <v>32.16</v>
       </c>
       <c r="G61">
         <v>10</v>
@@ -6289,28 +6289,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M61">
-        <v>2.2737656</v>
+        <v>2.312304</v>
       </c>
       <c r="N61">
-        <v>3.761234399999999</v>
+        <v>3.722695999999999</v>
       </c>
       <c r="O61">
-        <v>1.31643204</v>
+        <v>1.3029436</v>
       </c>
       <c r="P61">
-        <v>2.44480236</v>
+        <v>2.419752399999999</v>
       </c>
       <c r="Q61">
-        <v>8.48480236</v>
+        <v>8.459752399999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1662226964944229</v>
+        <v>0.1686888197685683</v>
       </c>
       <c r="T61">
-        <v>1.752296964586861</v>
+        <v>1.788182063105496</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.654187397328907</v>
+        <v>2.609950940706758</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09551652790742732</v>
+        <v>0.09530810025214125</v>
       </c>
       <c r="C62">
-        <v>25.64129662106063</v>
+        <v>25.30653868293778</v>
       </c>
       <c r="D62">
-        <v>47.80129662106062</v>
+        <v>48.00253868293778</v>
       </c>
       <c r="E62">
-        <v>13.06</v>
+        <v>13.596</v>
       </c>
       <c r="F62">
-        <v>32.16</v>
+        <v>32.696</v>
       </c>
       <c r="G62">
         <v>10</v>
@@ -6371,28 +6371,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M62">
-        <v>2.312304</v>
+        <v>2.3508424</v>
       </c>
       <c r="N62">
-        <v>3.722695999999999</v>
+        <v>3.684157599999999</v>
       </c>
       <c r="O62">
-        <v>1.3029436</v>
+        <v>1.28945516</v>
       </c>
       <c r="P62">
-        <v>2.419752399999999</v>
+        <v>2.39470244</v>
       </c>
       <c r="Q62">
-        <v>8.459752399999999</v>
+        <v>8.434702439999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1686888197685683</v>
+        <v>0.1712814109029263</v>
       </c>
       <c r="T62">
-        <v>1.788182063105496</v>
+        <v>1.825907423086625</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.609950940706758</v>
+        <v>2.567164859711565</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09530810025214125</v>
+        <v>0.09509967259685519</v>
       </c>
       <c r="C63">
-        <v>25.30653868293778</v>
+        <v>24.97348235494303</v>
       </c>
       <c r="D63">
-        <v>48.00253868293778</v>
+        <v>48.20548235494303</v>
       </c>
       <c r="E63">
-        <v>13.596</v>
+        <v>14.132</v>
       </c>
       <c r="F63">
-        <v>32.696</v>
+        <v>33.232</v>
       </c>
       <c r="G63">
         <v>10</v>
@@ -6453,28 +6453,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M63">
-        <v>2.3508424</v>
+        <v>2.3893808</v>
       </c>
       <c r="N63">
-        <v>3.684157599999999</v>
+        <v>3.645619199999999</v>
       </c>
       <c r="O63">
-        <v>1.28945516</v>
+        <v>1.27596672</v>
       </c>
       <c r="P63">
-        <v>2.39470244</v>
+        <v>2.36965248</v>
       </c>
       <c r="Q63">
-        <v>8.434702439999999</v>
+        <v>8.40965248</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1712814109029263</v>
+        <v>0.1740104542022505</v>
       </c>
       <c r="T63">
-        <v>1.825907423086625</v>
+        <v>1.865618328329918</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.567164859711565</v>
+        <v>2.525758974877507</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09509967259685519</v>
+        <v>0.0964882949415691</v>
       </c>
       <c r="C64">
-        <v>24.97348235494303</v>
+        <v>23.11687746947686</v>
       </c>
       <c r="D64">
-        <v>48.20548235494303</v>
+        <v>46.88487746947686</v>
       </c>
       <c r="E64">
-        <v>14.132</v>
+        <v>14.668</v>
       </c>
       <c r="F64">
-        <v>33.232</v>
+        <v>33.768</v>
       </c>
       <c r="G64">
         <v>10</v>
@@ -6535,45 +6535,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M64">
-        <v>2.3893808</v>
+        <v>2.5596144</v>
       </c>
       <c r="N64">
-        <v>3.645619199999999</v>
+        <v>3.475385599999999</v>
       </c>
       <c r="O64">
-        <v>1.27596672</v>
+        <v>1.21638496</v>
       </c>
       <c r="P64">
-        <v>2.36965248</v>
+        <v>2.25900064</v>
       </c>
       <c r="Q64">
-        <v>8.40965248</v>
+        <v>8.299000639999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1740104542022505</v>
+        <v>0.1768870133555922</v>
       </c>
       <c r="T64">
-        <v>1.865618328329918</v>
+        <v>1.907475768991768</v>
       </c>
       <c r="U64">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.35</v>
       </c>
       <c r="W64">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.525758974877507</v>
+        <v>2.357777015162909</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0964882949415691</v>
+        <v>0.09630521728628305</v>
       </c>
       <c r="C65">
-        <v>23.11687746947686</v>
+        <v>22.75083166226511</v>
       </c>
       <c r="D65">
-        <v>46.88487746947686</v>
+        <v>47.05483166226512</v>
       </c>
       <c r="E65">
-        <v>14.668</v>
+        <v>15.204</v>
       </c>
       <c r="F65">
-        <v>33.768</v>
+        <v>34.304</v>
       </c>
       <c r="G65">
         <v>10</v>
@@ -6617,28 +6617,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M65">
-        <v>2.5596144</v>
+        <v>2.6002432</v>
       </c>
       <c r="N65">
-        <v>3.475385599999999</v>
+        <v>3.434756799999999</v>
       </c>
       <c r="O65">
-        <v>1.21638496</v>
+        <v>1.20216488</v>
       </c>
       <c r="P65">
-        <v>2.25900064</v>
+        <v>2.232591919999999</v>
       </c>
       <c r="Q65">
-        <v>8.299000639999999</v>
+        <v>8.27259192</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1768870133555922</v>
+        <v>0.1799233813507862</v>
       </c>
       <c r="T65">
-        <v>1.907475768991768</v>
+        <v>1.95165862302372</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.357777015162909</v>
+        <v>2.320936749300988</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09630521728628305</v>
+        <v>0.09612213963099697</v>
       </c>
       <c r="C66">
-        <v>22.75083166226511</v>
+        <v>22.38602248033801</v>
       </c>
       <c r="D66">
-        <v>47.05483166226512</v>
+        <v>47.22602248033801</v>
       </c>
       <c r="E66">
-        <v>15.204</v>
+        <v>15.74</v>
       </c>
       <c r="F66">
-        <v>34.304</v>
+        <v>34.84</v>
       </c>
       <c r="G66">
         <v>10</v>
@@ -6699,28 +6699,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M66">
-        <v>2.6002432</v>
+        <v>2.640872</v>
       </c>
       <c r="N66">
-        <v>3.434756799999999</v>
+        <v>3.394127999999999</v>
       </c>
       <c r="O66">
-        <v>1.20216488</v>
+        <v>1.187944799999999</v>
       </c>
       <c r="P66">
-        <v>2.232591919999999</v>
+        <v>2.206183199999999</v>
       </c>
       <c r="Q66">
-        <v>8.27259192</v>
+        <v>8.246183199999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1799233813507862</v>
+        <v>0.1831332560885628</v>
       </c>
       <c r="T66">
-        <v>1.95165862302372</v>
+        <v>1.998366211571784</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.320936749300988</v>
+        <v>2.285230030080973</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09612213963099697</v>
+        <v>0.09593906197571089</v>
       </c>
       <c r="C67">
-        <v>22.38602248033801</v>
+        <v>22.02246346992764</v>
       </c>
       <c r="D67">
-        <v>47.22602248033801</v>
+        <v>47.39846346992765</v>
       </c>
       <c r="E67">
-        <v>15.74</v>
+        <v>16.276</v>
       </c>
       <c r="F67">
-        <v>34.84</v>
+        <v>35.376</v>
       </c>
       <c r="G67">
         <v>10</v>
@@ -6781,28 +6781,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M67">
-        <v>2.640872</v>
+        <v>2.681500800000001</v>
       </c>
       <c r="N67">
-        <v>3.394127999999999</v>
+        <v>3.353499199999999</v>
       </c>
       <c r="O67">
-        <v>1.187944799999999</v>
+        <v>1.173724719999999</v>
       </c>
       <c r="P67">
-        <v>2.206183199999999</v>
+        <v>2.179774479999999</v>
       </c>
       <c r="Q67">
-        <v>8.246183199999999</v>
+        <v>8.219774479999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1831332560885628</v>
+        <v>0.186531946987385</v>
       </c>
       <c r="T67">
-        <v>1.998366211571784</v>
+        <v>2.047821305328557</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.285230030080973</v>
+        <v>2.250605332655503</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09593906197571089</v>
+        <v>0.09575598432042484</v>
       </c>
       <c r="C68">
-        <v>22.02246346992764</v>
+        <v>21.66016837584196</v>
       </c>
       <c r="D68">
-        <v>47.39846346992765</v>
+        <v>47.57216837584196</v>
       </c>
       <c r="E68">
-        <v>16.276</v>
+        <v>16.812</v>
       </c>
       <c r="F68">
-        <v>35.376</v>
+        <v>35.91200000000001</v>
       </c>
       <c r="G68">
         <v>10</v>
@@ -6863,28 +6863,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M68">
-        <v>2.681500800000001</v>
+        <v>2.722129600000001</v>
       </c>
       <c r="N68">
-        <v>3.353499199999999</v>
+        <v>3.312870399999999</v>
       </c>
       <c r="O68">
-        <v>1.173724719999999</v>
+        <v>1.15950464</v>
       </c>
       <c r="P68">
-        <v>2.179774479999999</v>
+        <v>2.153365759999999</v>
       </c>
       <c r="Q68">
-        <v>8.219774479999998</v>
+        <v>8.193365759999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.186531946987385</v>
+        <v>0.1901366191528025</v>
       </c>
       <c r="T68">
-        <v>2.047821305328557</v>
+        <v>2.100273677494833</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.250605332655503</v>
+        <v>2.217014208287511</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09575598432042484</v>
+        <v>0.09557290666513876</v>
       </c>
       <c r="C69">
-        <v>21.66016837584196</v>
+        <v>21.29915114511679</v>
       </c>
       <c r="D69">
-        <v>47.57216837584196</v>
+        <v>47.74715114511679</v>
       </c>
       <c r="E69">
-        <v>16.812</v>
+        <v>17.348</v>
       </c>
       <c r="F69">
-        <v>35.91200000000001</v>
+        <v>36.448</v>
       </c>
       <c r="G69">
         <v>10</v>
@@ -6945,28 +6945,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M69">
-        <v>2.722129600000001</v>
+        <v>2.7627584</v>
       </c>
       <c r="N69">
-        <v>3.312870399999999</v>
+        <v>3.272241599999999</v>
       </c>
       <c r="O69">
-        <v>1.15950464</v>
+        <v>1.14528456</v>
       </c>
       <c r="P69">
-        <v>2.153365759999999</v>
+        <v>2.12695704</v>
       </c>
       <c r="Q69">
-        <v>8.193365759999999</v>
+        <v>8.16695704</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1901366191528025</v>
+        <v>0.1939665833285586</v>
       </c>
       <c r="T69">
-        <v>2.100273677494833</v>
+        <v>2.1560043229215</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.217014208287511</v>
+        <v>2.184411058165636</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09557290666513876</v>
+        <v>0.09538982900985268</v>
       </c>
       <c r="C70">
-        <v>21.29915114511679</v>
+        <v>20.93942593074875</v>
       </c>
       <c r="D70">
-        <v>47.74715114511679</v>
+        <v>47.92342593074876</v>
       </c>
       <c r="E70">
-        <v>17.348</v>
+        <v>17.884</v>
       </c>
       <c r="F70">
-        <v>36.448</v>
+        <v>36.984</v>
       </c>
       <c r="G70">
         <v>10</v>
@@ -7027,28 +7027,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M70">
-        <v>2.7627584</v>
+        <v>2.8033872</v>
       </c>
       <c r="N70">
-        <v>3.272241599999999</v>
+        <v>3.231612799999999</v>
       </c>
       <c r="O70">
-        <v>1.14528456</v>
+        <v>1.13106448</v>
       </c>
       <c r="P70">
-        <v>2.12695704</v>
+        <v>2.100548319999999</v>
       </c>
       <c r="Q70">
-        <v>8.16695704</v>
+        <v>8.140548319999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1939665833285586</v>
+        <v>0.1980436419672667</v>
       </c>
       <c r="T70">
-        <v>2.1560043229215</v>
+        <v>2.215330493859565</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.184411058165636</v>
+        <v>2.152752926887873</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09538982900985268</v>
+        <v>0.0952067513545666</v>
       </c>
       <c r="C71">
-        <v>20.93942593074875</v>
+        <v>20.5810070955113</v>
       </c>
       <c r="D71">
-        <v>47.92342593074876</v>
+        <v>48.10100709551131</v>
       </c>
       <c r="E71">
-        <v>17.884</v>
+        <v>18.42</v>
       </c>
       <c r="F71">
-        <v>36.984</v>
+        <v>37.52</v>
       </c>
       <c r="G71">
         <v>10</v>
@@ -7109,28 +7109,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M71">
-        <v>2.8033872</v>
+        <v>2.844016</v>
       </c>
       <c r="N71">
-        <v>3.231612799999999</v>
+        <v>3.190983999999999</v>
       </c>
       <c r="O71">
-        <v>1.13106448</v>
+        <v>1.1168444</v>
       </c>
       <c r="P71">
-        <v>2.100548319999999</v>
+        <v>2.0741396</v>
       </c>
       <c r="Q71">
-        <v>8.140548319999999</v>
+        <v>8.1141396</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1980436419672667</v>
+        <v>0.2023925045152221</v>
       </c>
       <c r="T71">
-        <v>2.215330493859565</v>
+        <v>2.278611742860168</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.152752926887873</v>
+        <v>2.121999313646618</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0952067513545666</v>
+        <v>0.09502367369928055</v>
       </c>
       <c r="C72">
-        <v>20.5810070955113</v>
+        <v>20.22390921585574</v>
       </c>
       <c r="D72">
-        <v>48.10100709551131</v>
+        <v>48.27990921585575</v>
       </c>
       <c r="E72">
-        <v>18.42</v>
+        <v>18.956</v>
       </c>
       <c r="F72">
-        <v>37.52</v>
+        <v>38.056</v>
       </c>
       <c r="G72">
         <v>10</v>
@@ -7191,28 +7191,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M72">
-        <v>2.844016</v>
+        <v>2.884644800000001</v>
       </c>
       <c r="N72">
-        <v>3.190983999999999</v>
+        <v>3.150355199999999</v>
       </c>
       <c r="O72">
-        <v>1.1168444</v>
+        <v>1.102624319999999</v>
       </c>
       <c r="P72">
-        <v>2.0741396</v>
+        <v>2.047730879999999</v>
       </c>
       <c r="Q72">
-        <v>8.1141396</v>
+        <v>8.087730879999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2023925045152221</v>
+        <v>0.2070412886182088</v>
       </c>
       <c r="T72">
-        <v>2.278611742860168</v>
+        <v>2.346257215929779</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.121999313646618</v>
+        <v>2.092111999369904</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09502367369928055</v>
+        <v>0.09484059604399447</v>
       </c>
       <c r="C73">
-        <v>20.22390921585575</v>
+        <v>19.86814708589987</v>
       </c>
       <c r="D73">
-        <v>48.27990921585575</v>
+        <v>48.46014708589987</v>
       </c>
       <c r="E73">
-        <v>18.956</v>
+        <v>19.492</v>
       </c>
       <c r="F73">
-        <v>38.056</v>
+        <v>38.592</v>
       </c>
       <c r="G73">
         <v>10</v>
@@ -7273,28 +7273,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M73">
-        <v>2.8846448</v>
+        <v>2.9252736</v>
       </c>
       <c r="N73">
-        <v>3.150355199999999</v>
+        <v>3.109726399999999</v>
       </c>
       <c r="O73">
-        <v>1.10262432</v>
+        <v>1.08840424</v>
       </c>
       <c r="P73">
-        <v>2.04773088</v>
+        <v>2.02132216</v>
       </c>
       <c r="Q73">
-        <v>8.087730879999999</v>
+        <v>8.06132216</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2070412886182088</v>
+        <v>0.2120221287285517</v>
       </c>
       <c r="T73">
-        <v>2.346257215929778</v>
+        <v>2.41873450850436</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.092111999369905</v>
+        <v>2.063054888267545</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09484059604399447</v>
+        <v>0.09465751838870839</v>
       </c>
       <c r="C74">
-        <v>19.86814708589987</v>
+        <v>19.51373572150595</v>
       </c>
       <c r="D74">
-        <v>48.46014708589987</v>
+        <v>48.64173572150595</v>
       </c>
       <c r="E74">
-        <v>19.492</v>
+        <v>20.028</v>
       </c>
       <c r="F74">
-        <v>38.592</v>
+        <v>39.128</v>
       </c>
       <c r="G74">
         <v>10</v>
@@ -7355,28 +7355,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M74">
-        <v>2.9252736</v>
+        <v>2.9659024</v>
       </c>
       <c r="N74">
-        <v>3.109726399999999</v>
+        <v>3.069097599999999</v>
       </c>
       <c r="O74">
-        <v>1.08840424</v>
+        <v>1.07418416</v>
       </c>
       <c r="P74">
-        <v>2.02132216</v>
+        <v>1.994913439999999</v>
       </c>
       <c r="Q74">
-        <v>8.06132216</v>
+        <v>8.03491344</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2120221287285517</v>
+        <v>0.2173719199581793</v>
       </c>
       <c r="T74">
-        <v>2.41873450850436</v>
+        <v>2.4965804894178</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.063054888267545</v>
+        <v>2.034793862400866</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09465751838870839</v>
+        <v>0.09447444073342233</v>
       </c>
       <c r="C75">
-        <v>19.51373572150595</v>
+        <v>19.1606903644511</v>
       </c>
       <c r="D75">
-        <v>48.64173572150595</v>
+        <v>48.8246903644511</v>
       </c>
       <c r="E75">
-        <v>20.028</v>
+        <v>20.564</v>
       </c>
       <c r="F75">
-        <v>39.128</v>
+        <v>39.664</v>
       </c>
       <c r="G75">
         <v>10</v>
@@ -7437,28 +7437,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M75">
-        <v>2.9659024</v>
+        <v>3.0065312</v>
       </c>
       <c r="N75">
-        <v>3.069097599999999</v>
+        <v>3.028468799999999</v>
       </c>
       <c r="O75">
-        <v>1.07418416</v>
+        <v>1.059964079999999</v>
       </c>
       <c r="P75">
-        <v>1.994913439999999</v>
+        <v>1.968504719999999</v>
       </c>
       <c r="Q75">
-        <v>8.03491344</v>
+        <v>8.008504719999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2173719199581793</v>
+        <v>0.2231332335900859</v>
       </c>
       <c r="T75">
-        <v>2.4965804894178</v>
+        <v>2.580414622709196</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.034793862400866</v>
+        <v>2.007296648044098</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09447444073342233</v>
+        <v>0.1012138630781363</v>
       </c>
       <c r="C76">
-        <v>19.1606903644511</v>
+        <v>12.6866418159869</v>
       </c>
       <c r="D76">
-        <v>48.8246903644511</v>
+        <v>42.8866418159869</v>
       </c>
       <c r="E76">
-        <v>20.564</v>
+        <v>21.1</v>
       </c>
       <c r="F76">
-        <v>39.664</v>
+        <v>40.2</v>
       </c>
       <c r="G76">
         <v>10</v>
@@ -7519,45 +7519,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M76">
-        <v>3.0065312</v>
+        <v>3.618</v>
       </c>
       <c r="N76">
-        <v>3.028468799999999</v>
+        <v>2.416999999999999</v>
       </c>
       <c r="O76">
-        <v>1.059964079999999</v>
+        <v>0.8459499999999995</v>
       </c>
       <c r="P76">
-        <v>1.968504719999999</v>
+        <v>1.571049999999999</v>
       </c>
       <c r="Q76">
-        <v>8.008504719999999</v>
+        <v>7.61105</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2231332335900859</v>
+        <v>0.2293554523125451</v>
       </c>
       <c r="T76">
-        <v>2.580414622709196</v>
+        <v>2.670955486663906</v>
       </c>
       <c r="U76">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V76">
         <v>0.35</v>
       </c>
       <c r="W76">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.007296648044098</v>
+        <v>1.668048645660586</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1012138630781363</v>
+        <v>0.1011230854228502</v>
       </c>
       <c r="C77">
-        <v>12.6866418159869</v>
+        <v>12.2210129595591</v>
       </c>
       <c r="D77">
-        <v>42.8866418159869</v>
+        <v>42.9570129595591</v>
       </c>
       <c r="E77">
-        <v>21.1</v>
+        <v>21.636</v>
       </c>
       <c r="F77">
-        <v>40.2</v>
+        <v>40.736</v>
       </c>
       <c r="G77">
         <v>10</v>
@@ -7601,28 +7601,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M77">
-        <v>3.618</v>
+        <v>3.66624</v>
       </c>
       <c r="N77">
-        <v>2.416999999999999</v>
+        <v>2.368759999999999</v>
       </c>
       <c r="O77">
-        <v>0.8459499999999995</v>
+        <v>0.8290659999999996</v>
       </c>
       <c r="P77">
-        <v>1.571049999999999</v>
+        <v>1.539693999999999</v>
       </c>
       <c r="Q77">
-        <v>7.61105</v>
+        <v>7.579694</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2293554523125451</v>
+        <v>0.2360961892618758</v>
       </c>
       <c r="T77">
-        <v>2.670955486663906</v>
+        <v>2.76904142261484</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.668048645660586</v>
+        <v>1.646100637165052</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1011230854228502</v>
+        <v>0.1010323077675641</v>
       </c>
       <c r="C78">
-        <v>12.2210129595591</v>
+        <v>11.7556154216357</v>
       </c>
       <c r="D78">
-        <v>42.9570129595591</v>
+        <v>43.02761542163571</v>
       </c>
       <c r="E78">
-        <v>21.636</v>
+        <v>22.172</v>
       </c>
       <c r="F78">
-        <v>40.736</v>
+        <v>41.27200000000001</v>
       </c>
       <c r="G78">
         <v>10</v>
@@ -7683,28 +7683,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M78">
-        <v>3.66624</v>
+        <v>3.71448</v>
       </c>
       <c r="N78">
-        <v>2.368759999999999</v>
+        <v>2.320519999999999</v>
       </c>
       <c r="O78">
-        <v>0.8290659999999996</v>
+        <v>0.8121819999999995</v>
       </c>
       <c r="P78">
-        <v>1.539693999999999</v>
+        <v>1.508337999999999</v>
       </c>
       <c r="Q78">
-        <v>7.579694</v>
+        <v>7.548337999999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2360961892618758</v>
+        <v>0.2434230772502788</v>
       </c>
       <c r="T78">
-        <v>2.76904142261484</v>
+        <v>2.875656570387595</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.646100637165052</v>
+        <v>1.624722706812259</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1010323077675641</v>
+        <v>0.100941530112278</v>
       </c>
       <c r="C79">
-        <v>11.7556154216357</v>
+        <v>11.29045034465241</v>
       </c>
       <c r="D79">
-        <v>43.02761542163571</v>
+        <v>43.09845034465241</v>
       </c>
       <c r="E79">
-        <v>22.172</v>
+        <v>22.708</v>
       </c>
       <c r="F79">
-        <v>41.27200000000001</v>
+        <v>41.808</v>
       </c>
       <c r="G79">
         <v>10</v>
@@ -7765,28 +7765,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M79">
-        <v>3.71448</v>
+        <v>3.76272</v>
       </c>
       <c r="N79">
-        <v>2.320519999999999</v>
+        <v>2.272279999999999</v>
       </c>
       <c r="O79">
-        <v>0.8121819999999995</v>
+        <v>0.7952979999999997</v>
       </c>
       <c r="P79">
-        <v>1.508337999999999</v>
+        <v>1.476982</v>
       </c>
       <c r="Q79">
-        <v>7.548337999999999</v>
+        <v>7.516982</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2434230772502788</v>
+        <v>0.2514160459649002</v>
       </c>
       <c r="T79">
-        <v>2.875656570387595</v>
+        <v>2.991964004321509</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.624722706812259</v>
+        <v>1.603892928519794</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.100941530112278</v>
+        <v>0.100850752456992</v>
       </c>
       <c r="C80">
-        <v>11.29045034465241</v>
+        <v>10.8255188785804</v>
       </c>
       <c r="D80">
-        <v>43.09845034465241</v>
+        <v>43.1695188785804</v>
       </c>
       <c r="E80">
-        <v>22.708</v>
+        <v>23.244</v>
       </c>
       <c r="F80">
-        <v>41.808</v>
+        <v>42.344</v>
       </c>
       <c r="G80">
         <v>10</v>
@@ -7847,28 +7847,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M80">
-        <v>3.76272</v>
+        <v>3.81096</v>
       </c>
       <c r="N80">
-        <v>2.272279999999999</v>
+        <v>2.224039999999999</v>
       </c>
       <c r="O80">
-        <v>0.7952979999999997</v>
+        <v>0.7784139999999996</v>
       </c>
       <c r="P80">
-        <v>1.476982</v>
+        <v>1.445625999999999</v>
       </c>
       <c r="Q80">
-        <v>7.516982</v>
+        <v>7.485626</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2514160459649002</v>
+        <v>0.2601702497951999</v>
       </c>
       <c r="T80">
-        <v>2.991964004321509</v>
+        <v>3.119348336725321</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.603892928519794</v>
+        <v>1.583590486386632</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.100850752456992</v>
+        <v>0.1007599748017059</v>
       </c>
       <c r="C81">
-        <v>10.8255188785804</v>
+        <v>10.36082218098846</v>
       </c>
       <c r="D81">
-        <v>43.1695188785804</v>
+        <v>43.24082218098846</v>
       </c>
       <c r="E81">
-        <v>23.244</v>
+        <v>23.78</v>
       </c>
       <c r="F81">
-        <v>42.344</v>
+        <v>42.88</v>
       </c>
       <c r="G81">
         <v>10</v>
@@ -7929,28 +7929,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M81">
-        <v>3.81096</v>
+        <v>3.8592</v>
       </c>
       <c r="N81">
-        <v>2.224039999999999</v>
+        <v>2.175799999999999</v>
       </c>
       <c r="O81">
-        <v>0.7784139999999996</v>
+        <v>0.7615299999999997</v>
       </c>
       <c r="P81">
-        <v>1.445625999999999</v>
+        <v>1.41427</v>
       </c>
       <c r="Q81">
-        <v>7.485626</v>
+        <v>7.454269999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2601702497951999</v>
+        <v>0.2697998740085296</v>
       </c>
       <c r="T81">
-        <v>3.119348336725321</v>
+        <v>3.259471102369512</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.583590486386632</v>
+        <v>1.563795605306799</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1007599748017059</v>
+        <v>0.1006691971464198</v>
       </c>
       <c r="C82">
-        <v>10.36082218098846</v>
+        <v>9.896361417105886</v>
       </c>
       <c r="D82">
-        <v>43.24082218098846</v>
+        <v>43.31236141710589</v>
       </c>
       <c r="E82">
-        <v>23.78</v>
+        <v>24.316</v>
       </c>
       <c r="F82">
-        <v>42.88</v>
+        <v>43.416</v>
       </c>
       <c r="G82">
         <v>10</v>
@@ -8011,28 +8011,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M82">
-        <v>3.8592</v>
+        <v>3.90744</v>
       </c>
       <c r="N82">
-        <v>2.175799999999999</v>
+        <v>2.127559999999999</v>
       </c>
       <c r="O82">
-        <v>0.7615299999999997</v>
+        <v>0.7446459999999996</v>
       </c>
       <c r="P82">
-        <v>1.41427</v>
+        <v>1.382914</v>
       </c>
       <c r="Q82">
-        <v>7.454269999999999</v>
+        <v>7.422914</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2697998740085296</v>
+        <v>0.2804431428758939</v>
       </c>
       <c r="T82">
-        <v>3.259471102369512</v>
+        <v>3.414343632818357</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.563795605306799</v>
+        <v>1.544489486722765</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1006691971464198</v>
+        <v>0.1005784194911338</v>
       </c>
       <c r="C83">
-        <v>9.896361417105886</v>
+        <v>9.43213775988599</v>
       </c>
       <c r="D83">
-        <v>43.31236141710589</v>
+        <v>43.38413775988599</v>
       </c>
       <c r="E83">
-        <v>24.316</v>
+        <v>24.852</v>
       </c>
       <c r="F83">
-        <v>43.416</v>
+        <v>43.95200000000001</v>
       </c>
       <c r="G83">
         <v>10</v>
@@ -8093,28 +8093,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M83">
-        <v>3.90744</v>
+        <v>3.955680000000001</v>
       </c>
       <c r="N83">
-        <v>2.127559999999999</v>
+        <v>2.079319999999999</v>
       </c>
       <c r="O83">
-        <v>0.7446459999999996</v>
+        <v>0.7277619999999995</v>
       </c>
       <c r="P83">
-        <v>1.382914</v>
+        <v>1.351557999999999</v>
       </c>
       <c r="Q83">
-        <v>7.422914</v>
+        <v>7.391558</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2804431428758939</v>
+        <v>0.2922689971729655</v>
       </c>
       <c r="T83">
-        <v>3.414343632818357</v>
+        <v>3.586424222205961</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.544489486722765</v>
+        <v>1.525654249079804</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1005784194911338</v>
+        <v>0.1004876418358477</v>
       </c>
       <c r="C84">
-        <v>9.43213775988599</v>
+        <v>8.968152390070117</v>
       </c>
       <c r="D84">
-        <v>43.38413775988599</v>
+        <v>43.45615239007012</v>
       </c>
       <c r="E84">
-        <v>24.852</v>
+        <v>25.38800000000001</v>
       </c>
       <c r="F84">
-        <v>43.95200000000001</v>
+        <v>44.48800000000001</v>
       </c>
       <c r="G84">
         <v>10</v>
@@ -8175,28 +8175,28 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M84">
-        <v>3.955680000000001</v>
+        <v>4.003920000000001</v>
       </c>
       <c r="N84">
-        <v>2.079319999999999</v>
+        <v>2.031079999999998</v>
       </c>
       <c r="O84">
-        <v>0.7277619999999995</v>
+        <v>0.7108779999999995</v>
       </c>
       <c r="P84">
-        <v>1.351557999999999</v>
+        <v>1.320201999999999</v>
       </c>
       <c r="Q84">
-        <v>7.391558</v>
+        <v>7.360201999999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2922689971729655</v>
+        <v>0.305486128446163</v>
       </c>
       <c r="T84">
-        <v>3.586424222205961</v>
+        <v>3.778749586815637</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.525654249079804</v>
+        <v>1.507272872584866</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1004876418358477</v>
+        <v>0.1367513354507873</v>
       </c>
       <c r="C85">
-        <v>8.968152390070117</v>
+        <v>-8.894482652142315</v>
       </c>
       <c r="D85">
-        <v>43.45615239007012</v>
+        <v>26.12951734785769</v>
       </c>
       <c r="E85">
-        <v>25.38800000000001</v>
+        <v>25.92400000000001</v>
       </c>
       <c r="F85">
-        <v>44.48800000000001</v>
+        <v>45.02400000000001</v>
       </c>
       <c r="G85">
         <v>10</v>
@@ -8257,45 +8257,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M85">
-        <v>4.003920000000001</v>
+        <v>6.609523200000002</v>
       </c>
       <c r="N85">
-        <v>2.031079999999998</v>
+        <v>-0.5745232000000025</v>
       </c>
       <c r="O85">
-        <v>0.7108779999999995</v>
+        <v>-0.2010831200000008</v>
       </c>
       <c r="P85">
-        <v>1.320201999999999</v>
+        <v>-0.3734400800000016</v>
       </c>
       <c r="Q85">
-        <v>7.360201999999999</v>
+        <v>5.666559919999998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.305486128446163</v>
+        <v>0.3302936544032415</v>
       </c>
       <c r="T85">
-        <v>3.778749586815637</v>
+        <v>4.13972931654218</v>
       </c>
       <c r="U85">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.35</v>
+        <v>0.3195767585776836</v>
       </c>
       <c r="W85">
-        <v>0.0585</v>
+        <v>0.09988613184079605</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.507272872584866</v>
+        <v>0.9130764530790962</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1367513354507873</v>
+        <v>0.1377613354507873</v>
       </c>
       <c r="C86">
-        <v>-8.894482652142301</v>
+        <v>-9.717459917010956</v>
       </c>
       <c r="D86">
-        <v>26.1295173478577</v>
+        <v>25.84254008298904</v>
       </c>
       <c r="E86">
-        <v>25.924</v>
+        <v>26.46</v>
       </c>
       <c r="F86">
-        <v>45.024</v>
+        <v>45.56</v>
       </c>
       <c r="G86">
         <v>10</v>
@@ -8339,37 +8339,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M86">
-        <v>6.609523200000001</v>
+        <v>6.688208000000001</v>
       </c>
       <c r="N86">
-        <v>-0.5745232000000016</v>
+        <v>-0.653208000000002</v>
       </c>
       <c r="O86">
-        <v>-0.2010831200000005</v>
+        <v>-0.2286228000000007</v>
       </c>
       <c r="P86">
-        <v>-0.3734400800000011</v>
+        <v>-0.4245852000000013</v>
       </c>
       <c r="Q86">
-        <v>5.666559919999999</v>
+        <v>5.615414799999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3302936544032413</v>
+        <v>0.349259898030124</v>
       </c>
       <c r="T86">
-        <v>4.139729316542177</v>
+        <v>4.415711270978322</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.3195767585776837</v>
+        <v>0.3158170320061815</v>
       </c>
       <c r="W86">
-        <v>0.09988613184079605</v>
+        <v>0.1004380597014926</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9130764530790964</v>
+        <v>0.9023343771605187</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1377613354507873</v>
+        <v>0.1387713354507873</v>
       </c>
       <c r="C87">
-        <v>-9.717459917010956</v>
+        <v>-10.53420199043892</v>
       </c>
       <c r="D87">
-        <v>25.84254008298904</v>
+        <v>25.56179800956109</v>
       </c>
       <c r="E87">
-        <v>26.46</v>
+        <v>26.996</v>
       </c>
       <c r="F87">
-        <v>45.56</v>
+        <v>46.096</v>
       </c>
       <c r="G87">
         <v>10</v>
@@ -8421,37 +8421,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M87">
-        <v>6.688208000000001</v>
+        <v>6.766892800000001</v>
       </c>
       <c r="N87">
-        <v>-0.653208000000002</v>
+        <v>-0.7318928000000016</v>
       </c>
       <c r="O87">
-        <v>-0.2286228000000007</v>
+        <v>-0.2561624800000005</v>
       </c>
       <c r="P87">
-        <v>-0.4245852000000013</v>
+        <v>-0.475730320000001</v>
       </c>
       <c r="Q87">
-        <v>5.615414799999999</v>
+        <v>5.564269679999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.349259898030124</v>
+        <v>0.3709356050322757</v>
       </c>
       <c r="T87">
-        <v>4.415711270978322</v>
+        <v>4.731119218905345</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.3158170320061815</v>
+        <v>0.3121447409363422</v>
       </c>
       <c r="W87">
-        <v>0.1004380597014926</v>
+        <v>0.100977152030545</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9023343771605187</v>
+        <v>0.8918421169609778</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1387713354507873</v>
+        <v>0.1397813354507873</v>
       </c>
       <c r="C88">
-        <v>-10.53420199043892</v>
+        <v>-11.34490989776776</v>
       </c>
       <c r="D88">
-        <v>25.56179800956109</v>
+        <v>25.28709010223224</v>
       </c>
       <c r="E88">
-        <v>26.996</v>
+        <v>27.532</v>
       </c>
       <c r="F88">
-        <v>46.096</v>
+        <v>46.632</v>
       </c>
       <c r="G88">
         <v>10</v>
@@ -8503,37 +8503,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M88">
-        <v>6.766892800000001</v>
+        <v>6.8455776</v>
       </c>
       <c r="N88">
-        <v>-0.7318928000000016</v>
+        <v>-0.8105776000000011</v>
       </c>
       <c r="O88">
-        <v>-0.2561624800000005</v>
+        <v>-0.2837021600000004</v>
       </c>
       <c r="P88">
-        <v>-0.475730320000001</v>
+        <v>-0.5268754400000007</v>
       </c>
       <c r="Q88">
-        <v>5.564269679999999</v>
+        <v>5.51312456</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3709356050322757</v>
+        <v>0.3959460361886046</v>
       </c>
       <c r="T88">
-        <v>4.731119218905345</v>
+        <v>5.095051466513449</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.3121447409363422</v>
+        <v>0.308556870350867</v>
       </c>
       <c r="W88">
-        <v>0.100977152030545</v>
+        <v>0.1015038514324927</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8918421169609778</v>
+        <v>0.8815910581453344</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1397813354507873</v>
+        <v>0.1407913354507873</v>
       </c>
       <c r="C89">
-        <v>-11.34490989776776</v>
+        <v>-12.14977611469221</v>
       </c>
       <c r="D89">
-        <v>25.28709010223224</v>
+        <v>25.01822388530779</v>
       </c>
       <c r="E89">
-        <v>27.532</v>
+        <v>28.068</v>
       </c>
       <c r="F89">
-        <v>46.632</v>
+        <v>47.168</v>
       </c>
       <c r="G89">
         <v>10</v>
@@ -8585,37 +8585,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M89">
-        <v>6.8455776</v>
+        <v>6.924262400000001</v>
       </c>
       <c r="N89">
-        <v>-0.8105776000000011</v>
+        <v>-0.8892624000000016</v>
       </c>
       <c r="O89">
-        <v>-0.2837021600000004</v>
+        <v>-0.3112418400000005</v>
       </c>
       <c r="P89">
-        <v>-0.5268754400000007</v>
+        <v>-0.578020560000001</v>
       </c>
       <c r="Q89">
-        <v>5.51312456</v>
+        <v>5.461979439999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3959460361886046</v>
+        <v>0.4251248725376551</v>
       </c>
       <c r="T89">
-        <v>5.095051466513449</v>
+        <v>5.519639088722904</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.308556870350867</v>
+        <v>0.305050542278698</v>
       </c>
       <c r="W89">
-        <v>0.1015038514324927</v>
+        <v>0.1020185803934871</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8815910581453344</v>
+        <v>0.8715729779391375</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1407913354507873</v>
+        <v>0.1418013354507873</v>
       </c>
       <c r="C90">
-        <v>-12.14977611469221</v>
+        <v>-12.94898501700081</v>
       </c>
       <c r="D90">
-        <v>25.01822388530779</v>
+        <v>24.75501498299919</v>
       </c>
       <c r="E90">
-        <v>28.068</v>
+        <v>28.604</v>
       </c>
       <c r="F90">
-        <v>47.168</v>
+        <v>47.704</v>
       </c>
       <c r="G90">
         <v>10</v>
@@ -8667,37 +8667,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M90">
-        <v>6.924262400000001</v>
+        <v>7.0029472</v>
       </c>
       <c r="N90">
-        <v>-0.8892624000000016</v>
+        <v>-0.9679472000000011</v>
       </c>
       <c r="O90">
-        <v>-0.3112418400000005</v>
+        <v>-0.3387815200000004</v>
       </c>
       <c r="P90">
-        <v>-0.578020560000001</v>
+        <v>-0.6291656800000007</v>
       </c>
       <c r="Q90">
-        <v>5.461979439999999</v>
+        <v>5.410834319999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4251248725376551</v>
+        <v>0.4596089518592601</v>
       </c>
       <c r="T90">
-        <v>5.519639088722904</v>
+        <v>6.021424460424986</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.305050542278698</v>
+        <v>0.3016230080957914</v>
       </c>
       <c r="W90">
-        <v>0.1020185803934871</v>
+        <v>0.1025217424115378</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8715729779391375</v>
+        <v>0.8617800231308326</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1418013354507873</v>
+        <v>0.1428113354507873</v>
       </c>
       <c r="C91">
-        <v>-12.94898501700081</v>
+        <v>-13.74271330222282</v>
       </c>
       <c r="D91">
-        <v>24.75501498299919</v>
+        <v>24.49728669777718</v>
       </c>
       <c r="E91">
-        <v>28.604</v>
+        <v>29.14</v>
       </c>
       <c r="F91">
-        <v>47.704</v>
+        <v>48.24</v>
       </c>
       <c r="G91">
         <v>10</v>
@@ -8749,37 +8749,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M91">
-        <v>7.0029472</v>
+        <v>7.081632000000001</v>
       </c>
       <c r="N91">
-        <v>-0.9679472000000011</v>
+        <v>-1.046632000000002</v>
       </c>
       <c r="O91">
-        <v>-0.3387815200000004</v>
+        <v>-0.3663212000000005</v>
       </c>
       <c r="P91">
-        <v>-0.6291656800000007</v>
+        <v>-0.6803108000000011</v>
       </c>
       <c r="Q91">
-        <v>5.410834319999999</v>
+        <v>5.359689199999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4596089518592601</v>
+        <v>0.5009898470451861</v>
       </c>
       <c r="T91">
-        <v>6.021424460424986</v>
+        <v>6.623566906467485</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.3016230080957914</v>
+        <v>0.2982716413391714</v>
       </c>
       <c r="W91">
-        <v>0.1025217424115378</v>
+        <v>0.1030137230514096</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8617800231308326</v>
+        <v>0.8522046895404899</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1428113354507873</v>
+        <v>0.1438213354507873</v>
       </c>
       <c r="C92">
-        <v>-13.74271330222282</v>
+        <v>-14.53113038520755</v>
       </c>
       <c r="D92">
-        <v>24.49728669777718</v>
+        <v>24.24486961479245</v>
       </c>
       <c r="E92">
-        <v>29.14</v>
+        <v>29.676</v>
       </c>
       <c r="F92">
-        <v>48.24</v>
+        <v>48.776</v>
       </c>
       <c r="G92">
         <v>10</v>
@@ -8831,37 +8831,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M92">
-        <v>7.081632000000001</v>
+        <v>7.160316800000001</v>
       </c>
       <c r="N92">
-        <v>-1.046632000000002</v>
+        <v>-1.125316800000002</v>
       </c>
       <c r="O92">
-        <v>-0.3663212000000005</v>
+        <v>-0.3938608800000007</v>
       </c>
       <c r="P92">
-        <v>-0.6803108000000011</v>
+        <v>-0.7314559200000013</v>
       </c>
       <c r="Q92">
-        <v>5.359689199999999</v>
+        <v>5.308544079999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5009898470451861</v>
+        <v>0.5515664967168736</v>
       </c>
       <c r="T92">
-        <v>6.623566906467485</v>
+        <v>7.359518784963875</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2982716413391714</v>
+        <v>0.2949939309947849</v>
       </c>
       <c r="W92">
-        <v>0.1030137230514096</v>
+        <v>0.1034948909299656</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8522046895404899</v>
+        <v>0.8428398028422427</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1438213354507873</v>
+        <v>0.1448313354507873</v>
       </c>
       <c r="C93">
-        <v>-14.53113038520755</v>
+        <v>-15.31439876949698</v>
       </c>
       <c r="D93">
-        <v>24.24486961479245</v>
+        <v>23.99760123050302</v>
       </c>
       <c r="E93">
-        <v>29.676</v>
+        <v>30.212</v>
       </c>
       <c r="F93">
-        <v>48.776</v>
+        <v>49.312</v>
       </c>
       <c r="G93">
         <v>10</v>
@@ -8913,37 +8913,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M93">
-        <v>7.160316800000001</v>
+        <v>7.239001600000002</v>
       </c>
       <c r="N93">
-        <v>-1.125316800000002</v>
+        <v>-1.204001600000002</v>
       </c>
       <c r="O93">
-        <v>-0.3938608800000007</v>
+        <v>-0.4214005600000008</v>
       </c>
       <c r="P93">
-        <v>-0.7314559200000013</v>
+        <v>-0.7826010400000016</v>
       </c>
       <c r="Q93">
-        <v>5.308544079999999</v>
+        <v>5.257398959999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5515664967168736</v>
+        <v>0.6147873088064829</v>
       </c>
       <c r="T93">
-        <v>7.359518784963875</v>
+        <v>8.27945863308436</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2949939309947849</v>
+        <v>0.2917874752231024</v>
       </c>
       <c r="W93">
-        <v>0.1034948909299656</v>
+        <v>0.1039655986372486</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8428398028422427</v>
+        <v>0.8336785006374356</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1448313354507873</v>
+        <v>0.1458413354507873</v>
       </c>
       <c r="C94">
-        <v>-15.31439876949698</v>
+        <v>-16.09267439620261</v>
       </c>
       <c r="D94">
-        <v>23.99760123050302</v>
+        <v>23.7553256037974</v>
       </c>
       <c r="E94">
-        <v>30.212</v>
+        <v>30.748</v>
       </c>
       <c r="F94">
-        <v>49.312</v>
+        <v>49.84800000000001</v>
       </c>
       <c r="G94">
         <v>10</v>
@@ -8995,37 +8995,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M94">
-        <v>7.239001600000002</v>
+        <v>7.317686400000001</v>
       </c>
       <c r="N94">
-        <v>-1.204001600000002</v>
+        <v>-1.282686400000002</v>
       </c>
       <c r="O94">
-        <v>-0.4214005600000008</v>
+        <v>-0.4489402400000007</v>
       </c>
       <c r="P94">
-        <v>-0.7826010400000016</v>
+        <v>-0.8337461600000013</v>
       </c>
       <c r="Q94">
-        <v>5.257398959999998</v>
+        <v>5.206253839999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6147873088064829</v>
+        <v>0.696071210064552</v>
       </c>
       <c r="T94">
-        <v>8.27945863308436</v>
+        <v>9.462238437810699</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2917874752231024</v>
+        <v>0.2886499754895207</v>
       </c>
       <c r="W94">
-        <v>0.1039655986372486</v>
+        <v>0.1044261835981384</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8336785006374356</v>
+        <v>0.824714215684345</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1458413354507873</v>
+        <v>0.1468513354507873</v>
       </c>
       <c r="C95">
-        <v>-16.09267439620261</v>
+        <v>-16.86610697196031</v>
       </c>
       <c r="D95">
-        <v>23.7553256037974</v>
+        <v>23.5178930280397</v>
       </c>
       <c r="E95">
-        <v>30.748</v>
+        <v>31.28400000000001</v>
       </c>
       <c r="F95">
-        <v>49.84800000000001</v>
+        <v>50.38400000000001</v>
       </c>
       <c r="G95">
         <v>10</v>
@@ -9077,37 +9077,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M95">
-        <v>7.317686400000001</v>
+        <v>7.396371200000002</v>
       </c>
       <c r="N95">
-        <v>-1.282686400000002</v>
+        <v>-1.361371200000002</v>
       </c>
       <c r="O95">
-        <v>-0.4489402400000007</v>
+        <v>-0.4764799200000008</v>
       </c>
       <c r="P95">
-        <v>-0.8337461600000013</v>
+        <v>-0.8848912800000016</v>
       </c>
       <c r="Q95">
-        <v>5.206253839999999</v>
+        <v>5.155108719999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.696071210064552</v>
+        <v>0.8044497450753108</v>
       </c>
       <c r="T95">
-        <v>9.462238437810699</v>
+        <v>11.03927817744582</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2886499754895207</v>
+        <v>0.2855792310694195</v>
       </c>
       <c r="W95">
-        <v>0.1044261835981384</v>
+        <v>0.1048769688790092</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.824714215684345</v>
+        <v>0.8159406601983413</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1468513354507873</v>
+        <v>0.1478613354507873</v>
       </c>
       <c r="C96">
-        <v>-16.86610697196031</v>
+        <v>-17.63484027741242</v>
       </c>
       <c r="D96">
-        <v>23.5178930280397</v>
+        <v>23.28515972258758</v>
       </c>
       <c r="E96">
-        <v>31.28400000000001</v>
+        <v>31.82</v>
       </c>
       <c r="F96">
-        <v>50.38400000000001</v>
+        <v>50.92</v>
       </c>
       <c r="G96">
         <v>10</v>
@@ -9159,37 +9159,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M96">
-        <v>7.396371200000002</v>
+        <v>7.475056000000001</v>
       </c>
       <c r="N96">
-        <v>-1.361371200000002</v>
+        <v>-1.440056000000002</v>
       </c>
       <c r="O96">
-        <v>-0.4764799200000008</v>
+        <v>-0.5040196000000007</v>
       </c>
       <c r="P96">
-        <v>-0.8848912800000016</v>
+        <v>-0.9360364000000013</v>
       </c>
       <c r="Q96">
-        <v>5.155108719999999</v>
+        <v>5.103963599999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8044497450753108</v>
+        <v>0.9561796940903734</v>
       </c>
       <c r="T96">
-        <v>11.03927817744582</v>
+        <v>13.24713381293499</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2855792310694195</v>
+        <v>0.2825731339002677</v>
       </c>
       <c r="W96">
-        <v>0.1048769688790092</v>
+        <v>0.1053182639434407</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8159406601983413</v>
+        <v>0.807351811143622</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1478613354507873</v>
+        <v>0.2052032325428388</v>
       </c>
       <c r="C97">
-        <v>-17.63484027741242</v>
+        <v>-26.54717751527721</v>
       </c>
       <c r="D97">
-        <v>23.28515972258758</v>
+        <v>14.90882248472279</v>
       </c>
       <c r="E97">
-        <v>31.82</v>
+        <v>32.356</v>
       </c>
       <c r="F97">
-        <v>50.92</v>
+        <v>51.456</v>
       </c>
       <c r="G97">
         <v>10</v>
@@ -9241,45 +9241,45 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M97">
-        <v>7.475056000000001</v>
+        <v>10.3323648</v>
       </c>
       <c r="N97">
-        <v>-1.440056000000002</v>
+        <v>-4.297364800000001</v>
       </c>
       <c r="O97">
-        <v>-0.5040196000000007</v>
+        <v>-1.50407768</v>
       </c>
       <c r="P97">
-        <v>-0.9360364000000013</v>
+        <v>-2.793287120000001</v>
       </c>
       <c r="Q97">
-        <v>5.103963599999998</v>
+        <v>3.246712879999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9561796940903734</v>
+        <v>1.296072044914255</v>
       </c>
       <c r="T97">
-        <v>13.24713381293499</v>
+        <v>18.19298166365608</v>
       </c>
       <c r="U97">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.2825731339002677</v>
+        <v>0.2044304513909536</v>
       </c>
       <c r="W97">
-        <v>0.1053182639434407</v>
+        <v>0.1597503653606965</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.807351811143622</v>
+        <v>0.584087003974153</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2052032325428387</v>
+        <v>0.2067532325428387</v>
       </c>
       <c r="C98">
-        <v>-26.5471775152772</v>
+        <v>-27.22675136270005</v>
       </c>
       <c r="D98">
-        <v>14.9088224847228</v>
+        <v>14.76524863729995</v>
       </c>
       <c r="E98">
-        <v>32.35599999999999</v>
+        <v>32.892</v>
       </c>
       <c r="F98">
-        <v>51.456</v>
+        <v>51.992</v>
       </c>
       <c r="G98">
         <v>10</v>
@@ -9323,37 +9323,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M98">
-        <v>10.3323648</v>
+        <v>10.4399936</v>
       </c>
       <c r="N98">
-        <v>-4.2973648</v>
+        <v>-4.4049936</v>
       </c>
       <c r="O98">
-        <v>-1.50407768</v>
+        <v>-1.54174776</v>
       </c>
       <c r="P98">
-        <v>-2.79328712</v>
+        <v>-2.86324584</v>
       </c>
       <c r="Q98">
-        <v>3.24671288</v>
+        <v>3.17675416</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.296072044914251</v>
+        <v>1.712829393219002</v>
       </c>
       <c r="T98">
-        <v>18.19298166365603</v>
+        <v>24.2573088848747</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.2044304513909536</v>
+        <v>0.2023229209642427</v>
       </c>
       <c r="W98">
-        <v>0.1597503653606965</v>
+        <v>0.1601735574703801</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5840870039741531</v>
+        <v>0.5780654884692649</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2067532325428387</v>
+        <v>0.2083032325428388</v>
       </c>
       <c r="C99">
-        <v>-27.22675136270005</v>
+        <v>-27.90358631736338</v>
       </c>
       <c r="D99">
-        <v>14.76524863729995</v>
+        <v>14.62441368263662</v>
       </c>
       <c r="E99">
-        <v>32.892</v>
+        <v>33.428</v>
       </c>
       <c r="F99">
-        <v>51.992</v>
+        <v>52.528</v>
       </c>
       <c r="G99">
         <v>10</v>
@@ -9405,37 +9405,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M99">
-        <v>10.4399936</v>
+        <v>10.5476224</v>
       </c>
       <c r="N99">
-        <v>-4.4049936</v>
+        <v>-4.512622400000001</v>
       </c>
       <c r="O99">
-        <v>-1.54174776</v>
+        <v>-1.57941784</v>
       </c>
       <c r="P99">
-        <v>-2.86324584</v>
+        <v>-2.933204560000001</v>
       </c>
       <c r="Q99">
-        <v>3.17675416</v>
+        <v>3.10679544</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.712829393219002</v>
+        <v>2.546344089828502</v>
       </c>
       <c r="T99">
-        <v>24.2573088848747</v>
+        <v>36.38596332731206</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.2023229209642427</v>
+        <v>0.2002584013625668</v>
       </c>
       <c r="W99">
-        <v>0.1601735574703801</v>
+        <v>0.1605881130063966</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5780654884692649</v>
+        <v>0.572166861035905</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2083032325428388</v>
+        <v>0.2098532325428388</v>
       </c>
       <c r="C100">
-        <v>-27.90358631736338</v>
+        <v>-28.57776001169865</v>
       </c>
       <c r="D100">
-        <v>14.62441368263662</v>
+        <v>14.48623998830135</v>
       </c>
       <c r="E100">
-        <v>33.428</v>
+        <v>33.964</v>
       </c>
       <c r="F100">
-        <v>52.528</v>
+        <v>53.064</v>
       </c>
       <c r="G100">
         <v>10</v>
@@ -9487,37 +9487,37 @@
         <v>6.034999999999999</v>
       </c>
       <c r="M100">
-        <v>10.5476224</v>
+        <v>10.6552512</v>
       </c>
       <c r="N100">
-        <v>-4.512622400000001</v>
+        <v>-4.620251200000001</v>
       </c>
       <c r="O100">
-        <v>-1.57941784</v>
+        <v>-1.61708792</v>
       </c>
       <c r="P100">
-        <v>-2.933204560000001</v>
+        <v>-3.003163280000001</v>
       </c>
       <c r="Q100">
-        <v>3.10679544</v>
+        <v>3.036836719999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.546344089828502</v>
+        <v>5.046888179657005</v>
       </c>
       <c r="T100">
-        <v>36.38596332731206</v>
+        <v>72.77192665462411</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.2002584013625668</v>
+        <v>0.1982355892275913</v>
       </c>
       <c r="W100">
-        <v>0.1605881130063966</v>
+        <v>0.1609942936830997</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.572166861035905</v>
+        <v>0.5663873977931181</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2098532325428388</v>
-      </c>
-      <c r="C101">
-        <v>-28.57776001169865</v>
-      </c>
-      <c r="D101">
-        <v>14.48623998830135</v>
-      </c>
-      <c r="E101">
-        <v>33.964</v>
-      </c>
-      <c r="F101">
-        <v>53.064</v>
-      </c>
-      <c r="G101">
-        <v>10</v>
-      </c>
-      <c r="H101">
-        <v>34.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.075</v>
-      </c>
-      <c r="K101">
-        <v>6.04</v>
-      </c>
-      <c r="L101">
-        <v>6.034999999999999</v>
-      </c>
-      <c r="M101">
-        <v>10.6552512</v>
-      </c>
-      <c r="N101">
-        <v>-4.620251200000001</v>
-      </c>
-      <c r="O101">
-        <v>-1.61708792</v>
-      </c>
-      <c r="P101">
-        <v>-3.003163280000001</v>
-      </c>
-      <c r="Q101">
-        <v>3.036836719999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.046888179657005</v>
-      </c>
-      <c r="T101">
-        <v>72.77192665462411</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1982355892275913</v>
-      </c>
-      <c r="W101">
-        <v>0.1609942936830997</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5663873977931181</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
